--- a/CMAP_variableMetadata_additions.xlsx
+++ b/CMAP_variableMetadata_additions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\GitHub_niskin\BWrepos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063E24C3-D25B-4B98-BD50-985157914FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE99FE7-0508-4142-ABBA-857D7F693042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="1050" windowWidth="28575" windowHeight="19110" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="1620" windowWidth="31080" windowHeight="17355" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="4" r:id="rId1"/>
@@ -21,13 +21,30 @@
     <sheet name="964684_v1_amino_acids_biosscope" sheetId="9" r:id="rId6"/>
     <sheet name="920443_v1_biosscope_in_situ_pum" sheetId="10" r:id="rId7"/>
     <sheet name="PVST_BATS_PLANKTON" sheetId="11" r:id="rId8"/>
+    <sheet name="all_temp" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">PVST_BATS_PLANKTON!$A$5:$I$72</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="553">
   <si>
     <t>Program</t>
   </si>
@@ -1232,443 +1249,467 @@
     <t>BIOS-SCOPE, BIOS, Simons Foundation International, bio, biogeo, biogeochemistry, biology, flowCAM, Zooscan, net tows, Discrete, Bottle, cruise, Discrete, in situ, insitu, in-situ, North Atlantic Ocean, observation</t>
   </si>
   <si>
+    <t>degrees</t>
+  </si>
+  <si>
+    <t>lon</t>
+  </si>
+  <si>
+    <t>Sample longitude (decimal fractions; -180 to 180)</t>
+  </si>
+  <si>
+    <t>depth</t>
+  </si>
+  <si>
+    <t>Depth of measurement</t>
+  </si>
+  <si>
+    <t>hplc_gsfc_id</t>
+  </si>
+  <si>
+    <t>NASA GSFC HPLC processing idenfication number (i.e. 'GSFC HPLC lab sampler code')</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>station</t>
+  </si>
+  <si>
+    <t>Sample station</t>
+  </si>
+  <si>
+    <t>water_depth</t>
+  </si>
+  <si>
+    <t>The water (bottom) depth where the data were collected</t>
+  </si>
+  <si>
+    <t>bottle</t>
+  </si>
+  <si>
+    <t>Number used to identify a specific bottle within an array of bottle samples collected</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Sample date</t>
+  </si>
+  <si>
+    <t>yyyymmdd</t>
+  </si>
+  <si>
+    <t>volfilt</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>Sample number</t>
+  </si>
+  <si>
+    <t>allo</t>
+  </si>
+  <si>
+    <t>mg/m^3</t>
+  </si>
+  <si>
+    <t>alpha-beta-car</t>
+  </si>
+  <si>
+    <t>but-fuco</t>
+  </si>
+  <si>
+    <t>chl_c1c2</t>
+  </si>
+  <si>
+    <t>chl_c3</t>
+  </si>
+  <si>
+    <t>chlide_a</t>
+  </si>
+  <si>
+    <t>diadino</t>
+  </si>
+  <si>
+    <t>diato</t>
+  </si>
+  <si>
+    <t>dp</t>
+  </si>
+  <si>
+    <t>Total diagnostic pigments (PSC + Allo + Zea + Tot_Chl_b)</t>
+  </si>
+  <si>
+    <t>dv_chl_a</t>
+  </si>
+  <si>
+    <t>dv_chl_b</t>
+  </si>
+  <si>
+    <t>fuco</t>
+  </si>
+  <si>
+    <t>gyro</t>
+  </si>
+  <si>
+    <t>hex-fuco</t>
+  </si>
+  <si>
+    <t>lut</t>
+  </si>
+  <si>
+    <t>mv_chl_a</t>
+  </si>
+  <si>
+    <t>mv_chl_b</t>
+  </si>
+  <si>
+    <t>neo</t>
+  </si>
+  <si>
+    <t>perid</t>
+  </si>
+  <si>
+    <t>phide_a</t>
+  </si>
+  <si>
+    <t>phytin_a</t>
+  </si>
+  <si>
+    <t>ppc</t>
+  </si>
+  <si>
+    <t>Photoprotective carotenoids (Allo + Diadino + Diato + Zeo + alpha-beta-Car)</t>
+  </si>
+  <si>
+    <t>ppc_tcar</t>
+  </si>
+  <si>
+    <t>Ratio of PPC to Tcar</t>
+  </si>
+  <si>
+    <t>ppc_tpg</t>
+  </si>
+  <si>
+    <t>Ratio of PPC to Tpg</t>
+  </si>
+  <si>
+    <t>pras</t>
+  </si>
+  <si>
+    <t>psc</t>
+  </si>
+  <si>
+    <t>Photosynthetic carotenoids (But-fuco + Fuco + Hex-fuco + Perid)</t>
+  </si>
+  <si>
+    <t>psc_tcar</t>
+  </si>
+  <si>
+    <t>Ratio of PSC to Tcar</t>
+  </si>
+  <si>
+    <t>psp</t>
+  </si>
+  <si>
+    <t>Photosynthetic pigments (PSC + Tchl)</t>
+  </si>
+  <si>
+    <t>psp_tpg</t>
+  </si>
+  <si>
+    <t>Ratio of PSP to Tpg</t>
+  </si>
+  <si>
+    <t>tacc</t>
+  </si>
+  <si>
+    <t>Total accessory pigments (PPC + PSC + Tot_Chl_b + Tot_Chl_c)</t>
+  </si>
+  <si>
+    <t>tacc_tchla</t>
+  </si>
+  <si>
+    <t>Ratio of Tacc to Tot_Chl_a</t>
+  </si>
+  <si>
+    <t>tcar</t>
+  </si>
+  <si>
+    <t>Total carotenoids (PPC + PSC)</t>
+  </si>
+  <si>
+    <t>tchl</t>
+  </si>
+  <si>
+    <t>Tot_Chl_a + Tot_Chl_b + Tot_Chl_c</t>
+  </si>
+  <si>
+    <t>tchl_tcar</t>
+  </si>
+  <si>
+    <t>Ratio of Tchl to Tcar</t>
+  </si>
+  <si>
+    <t>tchla_tpg</t>
+  </si>
+  <si>
+    <t>Ratio of Tot_chl_a to Tpg</t>
+  </si>
+  <si>
+    <t>tot_chl_a</t>
+  </si>
+  <si>
+    <t>tot_chl_b</t>
+  </si>
+  <si>
+    <t>tot_chl_c</t>
+  </si>
+  <si>
+    <t>tpg</t>
+  </si>
+  <si>
+    <t>Total pigment concentration</t>
+  </si>
+  <si>
+    <t>viola</t>
+  </si>
+  <si>
+    <t>zea</t>
+  </si>
+  <si>
+    <t>objectdetails</t>
+  </si>
+  <si>
+    <t>associated_files</t>
+  </si>
+  <si>
+    <t>associated_file_types</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>Volume used in experiment</t>
+  </si>
+  <si>
+    <t>data_provider_category_manual</t>
+  </si>
+  <si>
+    <t>A category used by the data provider to name the organism or particle for a manual identification, not necessarily a scientific name.</t>
+  </si>
+  <si>
+    <t>scientificname_manual</t>
+  </si>
+  <si>
+    <t>A scientific name from a recognized taxonomic reference database (e.g., World Register of Marine Species, AlgaeBase) at the lowest level that matches the data provider's category, for a manual identification matched to scientificNameID. Generally, the ROI corresponds to an occurrence assigned to a single taxonomic name.</t>
+  </si>
+  <si>
+    <t>scientificnameid_manual</t>
+  </si>
+  <si>
+    <t>area_cross_section</t>
+  </si>
+  <si>
+    <t>um^2</t>
+  </si>
+  <si>
+    <t>length_representation</t>
+  </si>
+  <si>
+    <t>um</t>
+  </si>
+  <si>
+    <t>width_representation</t>
+  </si>
+  <si>
+    <t>equivalent_spherical_diameter</t>
+  </si>
+  <si>
+    <t>volume_sampled_ml</t>
+  </si>
+  <si>
+    <t>Volume sample by flow cytometer in milliliters</t>
+  </si>
+  <si>
+    <t>mL</t>
+  </si>
+  <si>
+    <t>volume_imaged_ml</t>
+  </si>
+  <si>
+    <t>Volume imaged by imaging flow cytometer in milliliters</t>
+  </si>
+  <si>
+    <t>volnet</t>
+  </si>
+  <si>
+    <t>splitfraction</t>
+  </si>
+  <si>
+    <t>particle_dilution_factor</t>
+  </si>
+  <si>
+    <t>biovolume</t>
+  </si>
+  <si>
+    <t>Biovolume for the target detected within the ROI determined by means specified in the biovolume calculation method or protocol document.</t>
+  </si>
+  <si>
+    <t>um^3</t>
+  </si>
+  <si>
+    <t>File type of an associated file.</t>
+  </si>
+  <si>
+    <t>the number of the image in EcoTaxa which is found as follows:  https://ecotaxa.obs-vlfr.fr/objectdetails/ &amp; objid (objid = the number of the image in EcoTaxa)</t>
+  </si>
+  <si>
+    <t>object_length, in um, major; Representation of length of the target detected within the ROI or largest mesh size for which the target could be retained, determined by means specified in the image processing method or protocol document.</t>
+  </si>
+  <si>
+    <t>object_width, in um, minor; Representation of width of the target detected within the ROI or smallest mesh size through which the target could pass, determined by means specified in the image processing method or protocol document.</t>
+  </si>
+  <si>
+    <t>object_diameter_esd ; Equivalent spherical diameter of the target detected within the ROI determined by means specified in the image processing method or protocol document.</t>
+  </si>
+  <si>
+    <t>File name of an associated file</t>
+  </si>
+  <si>
+    <t>object_area_filled; Cross-sectional area of the target detected within the ROI determined by means specified in the image processing method or protocol document.</t>
+  </si>
+  <si>
+    <t>A life science identifier from a recognized taxonomic reference database (e.g., World Register of Marine Species, AlgaeBase) at the lowest level that matches the data provider's category, for a manual identification matched to scientificNameID. Generally, the ROI corresponds to an occurrence assigned to a single taxonomic name.</t>
+  </si>
+  <si>
+    <t>the fraction of the sample that was diluted (for example if you split the sample 4 times that is 1/16th of the total sample so 16 is the value used)</t>
+  </si>
+  <si>
+    <t>volume calculated from net flowmeter in L</t>
+  </si>
+  <si>
+    <t>Term to encompass the conversion from particles to particles/mL - in this case the volume (in mL) the net sample is diluted into before passing it through the FlowCam</t>
+  </si>
+  <si>
+    <t>FlowCam</t>
+  </si>
+  <si>
+    <t>HPLC</t>
+  </si>
+  <si>
+    <t>Alloxanthin</t>
+  </si>
+  <si>
+    <t>Alpha (Beta,epsilon) + Beta (Beta,beta) Carotenes</t>
+  </si>
+  <si>
+    <t>19'-Butanoyloxyfucoxanthin</t>
+  </si>
+  <si>
+    <t>Chlorophyll c1 + c2 + Mg_DVP</t>
+  </si>
+  <si>
+    <t>Chlorophyll c3</t>
+  </si>
+  <si>
+    <t>Chlorophyllide a</t>
+  </si>
+  <si>
+    <t>Diadinoxanthin</t>
+  </si>
+  <si>
+    <t>Diatoxanthin</t>
+  </si>
+  <si>
+    <t>Divinyl Chorophyll a</t>
+  </si>
+  <si>
+    <t>Divinyl Chorophyll b</t>
+  </si>
+  <si>
+    <t>Fucoxanthin</t>
+  </si>
+  <si>
+    <t>Gyroxanthin-Diester</t>
+  </si>
+  <si>
+    <t>19'-Hexanoyloxyfucoxanthin</t>
+  </si>
+  <si>
+    <t>Lutein</t>
+  </si>
+  <si>
+    <t>Monovinyl Chorophyll a</t>
+  </si>
+  <si>
+    <t>Monovinyl Chorophyll b</t>
+  </si>
+  <si>
+    <t>Neoxanthin</t>
+  </si>
+  <si>
+    <t>Peridinin</t>
+  </si>
+  <si>
+    <t>Pheophorbide a</t>
+  </si>
+  <si>
+    <t>Pheophytin a</t>
+  </si>
+  <si>
+    <t>Prasinoxanthin</t>
+  </si>
+  <si>
+    <t>DV_Chl_a + MV_Chl_a + Chlide_a + Chl_a_allom + Chl_a_prime</t>
+  </si>
+  <si>
+    <t>DV_Chl_b + MV_Chl_b</t>
+  </si>
+  <si>
+    <t>chl_c1 + chl_c2 (i.e., chl_c1c2) + chl_c3</t>
+  </si>
+  <si>
+    <t>Violaxanthin</t>
+  </si>
+  <si>
+    <t>Zeaxanthin</t>
+  </si>
+  <si>
+    <t>Biovolume (total) for the group where group is from data_provider_category_manual</t>
+  </si>
+  <si>
     <t>lat</t>
   </si>
   <si>
     <t>Sample latitude (decimal fractions; -90 to 90)</t>
   </si>
   <si>
-    <t>degrees</t>
-  </si>
-  <si>
-    <t>lon</t>
-  </si>
-  <si>
-    <t>Sample longitude (decimal fractions; -180 to 180)</t>
-  </si>
-  <si>
-    <t>depth</t>
-  </si>
-  <si>
-    <t>Depth of measurement</t>
-  </si>
-  <si>
-    <t>hplc_gsfc_id</t>
-  </si>
-  <si>
-    <t>NASA GSFC HPLC processing idenfication number (i.e. 'GSFC HPLC lab sampler code')</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>station</t>
-  </si>
-  <si>
-    <t>Sample station</t>
-  </si>
-  <si>
-    <t>water_depth</t>
-  </si>
-  <si>
-    <t>The water (bottom) depth where the data were collected</t>
-  </si>
-  <si>
-    <t>bottle</t>
-  </si>
-  <si>
-    <t>Number used to identify a specific bottle within an array of bottle samples collected</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>Sample date</t>
-  </si>
-  <si>
-    <t>yyyymmdd</t>
-  </si>
-  <si>
-    <t>volfilt</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>sample</t>
-  </si>
-  <si>
-    <t>Sample number</t>
-  </si>
-  <si>
-    <t>allo</t>
-  </si>
-  <si>
-    <t>HPLC Alloxanthin</t>
-  </si>
-  <si>
-    <t>mg/m^3</t>
-  </si>
-  <si>
-    <t>alpha-beta-car</t>
-  </si>
-  <si>
-    <t>HPLC Alpha (Beta,epsilon) + Beta (Beta,beta) Carotenes</t>
-  </si>
-  <si>
-    <t>but-fuco</t>
-  </si>
-  <si>
-    <t>HPLC 19'-Butanoyloxyfucoxanthin</t>
-  </si>
-  <si>
-    <t>chl_c1c2</t>
-  </si>
-  <si>
-    <t>HPLC Chlorophyll c1 + c2 + Mg_DVP</t>
-  </si>
-  <si>
-    <t>chl_c3</t>
-  </si>
-  <si>
-    <t>HPLC Chlorophyll c3</t>
-  </si>
-  <si>
-    <t>chlide_a</t>
-  </si>
-  <si>
-    <t>HPLC Chlorophyllide a</t>
-  </si>
-  <si>
-    <t>diadino</t>
-  </si>
-  <si>
-    <t>HPLC Diadinoxanthin</t>
-  </si>
-  <si>
-    <t>diato</t>
-  </si>
-  <si>
-    <t>HPLC Diatoxanthin</t>
-  </si>
-  <si>
-    <t>dp</t>
-  </si>
-  <si>
-    <t>Total diagnostic pigments (PSC + Allo + Zea + Tot_Chl_b)</t>
-  </si>
-  <si>
-    <t>dv_chl_a</t>
-  </si>
-  <si>
-    <t>HPLC Divinyl Chorophyll a</t>
-  </si>
-  <si>
-    <t>dv_chl_b</t>
-  </si>
-  <si>
-    <t>HPLC Divinyl Chorophyll b</t>
-  </si>
-  <si>
-    <t>fuco</t>
-  </si>
-  <si>
-    <t>HPLC Fucoxanthin</t>
-  </si>
-  <si>
-    <t>gyro</t>
-  </si>
-  <si>
-    <t>HPLC Gyroxanthin-Diester</t>
-  </si>
-  <si>
-    <t>hex-fuco</t>
-  </si>
-  <si>
-    <t>HPLC 19'-Hexanoyloxyfucoxanthin</t>
-  </si>
-  <si>
-    <t>lut</t>
-  </si>
-  <si>
-    <t>HPLC Lutein</t>
-  </si>
-  <si>
-    <t>mv_chl_a</t>
-  </si>
-  <si>
-    <t>HPLC Monovinyl Chorophyll a</t>
-  </si>
-  <si>
-    <t>mv_chl_b</t>
-  </si>
-  <si>
-    <t>HPLC Monovinyl Chorophyll b</t>
-  </si>
-  <si>
-    <t>neo</t>
-  </si>
-  <si>
-    <t>HPLC Neoxanthin</t>
-  </si>
-  <si>
-    <t>perid</t>
-  </si>
-  <si>
-    <t>HPLC Peridinin</t>
-  </si>
-  <si>
-    <t>phide_a</t>
-  </si>
-  <si>
-    <t>HPLC Pheophorbide a</t>
-  </si>
-  <si>
-    <t>phytin_a</t>
-  </si>
-  <si>
-    <t>HPLC Pheophytin a</t>
-  </si>
-  <si>
-    <t>ppc</t>
-  </si>
-  <si>
-    <t>Photoprotective carotenoids (Allo + Diadino + Diato + Zeo + alpha-beta-Car)</t>
-  </si>
-  <si>
-    <t>ppc_tcar</t>
-  </si>
-  <si>
-    <t>Ratio of PPC to Tcar</t>
-  </si>
-  <si>
-    <t>ppc_tpg</t>
-  </si>
-  <si>
-    <t>Ratio of PPC to Tpg</t>
-  </si>
-  <si>
-    <t>pras</t>
-  </si>
-  <si>
-    <t>HPLC Prasinoxanthin</t>
-  </si>
-  <si>
-    <t>psc</t>
-  </si>
-  <si>
-    <t>Photosynthetic carotenoids (But-fuco + Fuco + Hex-fuco + Perid)</t>
-  </si>
-  <si>
-    <t>psc_tcar</t>
-  </si>
-  <si>
-    <t>Ratio of PSC to Tcar</t>
-  </si>
-  <si>
-    <t>psp</t>
-  </si>
-  <si>
-    <t>Photosynthetic pigments (PSC + Tchl)</t>
-  </si>
-  <si>
-    <t>psp_tpg</t>
-  </si>
-  <si>
-    <t>Ratio of PSP to Tpg</t>
-  </si>
-  <si>
-    <t>tacc</t>
-  </si>
-  <si>
-    <t>Total accessory pigments (PPC + PSC + Tot_Chl_b + Tot_Chl_c)</t>
-  </si>
-  <si>
-    <t>tacc_tchla</t>
-  </si>
-  <si>
-    <t>Ratio of Tacc to Tot_Chl_a</t>
-  </si>
-  <si>
-    <t>tcar</t>
-  </si>
-  <si>
-    <t>Total carotenoids (PPC + PSC)</t>
-  </si>
-  <si>
-    <t>tchl</t>
-  </si>
-  <si>
-    <t>Tot_Chl_a + Tot_Chl_b + Tot_Chl_c</t>
-  </si>
-  <si>
-    <t>tchl_tcar</t>
-  </si>
-  <si>
-    <t>Ratio of Tchl to Tcar</t>
-  </si>
-  <si>
-    <t>tchla_tpg</t>
-  </si>
-  <si>
-    <t>Ratio of Tot_chl_a to Tpg</t>
-  </si>
-  <si>
-    <t>tot_chl_a</t>
-  </si>
-  <si>
-    <t>HPLC DV_Chl_a + MV_Chl_a + Chlide_a + Chl_a_allom + Chl_a_prime</t>
-  </si>
-  <si>
-    <t>tot_chl_b</t>
-  </si>
-  <si>
-    <t>HPLC DV_Chl_b + MV_Chl_b</t>
-  </si>
-  <si>
-    <t>tot_chl_c</t>
-  </si>
-  <si>
-    <t>HPLC chl_c1 + chl_c2 (i.e., chl_c1c2) + chl_c3</t>
-  </si>
-  <si>
-    <t>tpg</t>
-  </si>
-  <si>
-    <t>Total pigment concentration</t>
-  </si>
-  <si>
-    <t>viola</t>
-  </si>
-  <si>
-    <t>HPLC Violaxanthin</t>
-  </si>
-  <si>
-    <t>zea</t>
-  </si>
-  <si>
-    <t>HPLC Zeaxanthin</t>
-  </si>
-  <si>
-    <t>objectdetails</t>
-  </si>
-  <si>
-    <t>associated_files</t>
-  </si>
-  <si>
-    <t>associated_file_types</t>
-  </si>
-  <si>
-    <t>volume</t>
-  </si>
-  <si>
-    <t>Volume used in experiment</t>
-  </si>
-  <si>
-    <t>data_provider_category_manual</t>
-  </si>
-  <si>
-    <t>A category used by the data provider to name the organism or particle for a manual identification, not necessarily a scientific name.</t>
-  </si>
-  <si>
-    <t>scientificname_manual</t>
-  </si>
-  <si>
-    <t>A scientific name from a recognized taxonomic reference database (e.g., World Register of Marine Species, AlgaeBase) at the lowest level that matches the data provider's category, for a manual identification matched to scientificNameID. Generally, the ROI corresponds to an occurrence assigned to a single taxonomic name.</t>
-  </si>
-  <si>
-    <t>scientificnameid_manual</t>
-  </si>
-  <si>
-    <t>area_cross_section</t>
-  </si>
-  <si>
-    <t>um^2</t>
-  </si>
-  <si>
-    <t>length_representation</t>
-  </si>
-  <si>
-    <t>um</t>
-  </si>
-  <si>
-    <t>width_representation</t>
-  </si>
-  <si>
-    <t>equivalent_spherical_diameter</t>
-  </si>
-  <si>
-    <t>volume_sampled_ml</t>
-  </si>
-  <si>
-    <t>Volume sample by flow cytometer in milliliters</t>
-  </si>
-  <si>
-    <t>mL</t>
-  </si>
-  <si>
-    <t>volume_imaged_ml</t>
-  </si>
-  <si>
-    <t>Volume imaged by imaging flow cytometer in milliliters</t>
-  </si>
-  <si>
-    <t>volnet</t>
-  </si>
-  <si>
-    <t>splitfraction</t>
-  </si>
-  <si>
-    <t>particle_dilution_factor</t>
-  </si>
-  <si>
-    <t>biovolume</t>
-  </si>
-  <si>
-    <t>Biovolume for the target detected within the ROI determined by means specified in the biovolume calculation method or protocol document.</t>
-  </si>
-  <si>
-    <t>um^3</t>
-  </si>
-  <si>
-    <t>File type of an associated file.</t>
-  </si>
-  <si>
-    <t>the number of the image in EcoTaxa which is found as follows:  https://ecotaxa.obs-vlfr.fr/objectdetails/ &amp; objid (objid = the number of the image in EcoTaxa)</t>
-  </si>
-  <si>
-    <t>object_length, in um, major; Representation of length of the target detected within the ROI or largest mesh size for which the target could be retained, determined by means specified in the image processing method or protocol document.</t>
-  </si>
-  <si>
-    <t>object_width, in um, minor; Representation of width of the target detected within the ROI or smallest mesh size through which the target could pass, determined by means specified in the image processing method or protocol document.</t>
-  </si>
-  <si>
-    <t>object_diameter_esd ; Equivalent spherical diameter of the target detected within the ROI determined by means specified in the image processing method or protocol document.</t>
-  </si>
-  <si>
-    <t>File name of an associated file</t>
-  </si>
-  <si>
-    <t>object_area_filled; Cross-sectional area of the target detected within the ROI determined by means specified in the image processing method or protocol document.</t>
-  </si>
-  <si>
-    <t>A life science identifier from a recognized taxonomic reference database (e.g., World Register of Marine Species, AlgaeBase) at the lowest level that matches the data provider's category, for a manual identification matched to scientificNameID. Generally, the ROI corresponds to an occurrence assigned to a single taxonomic name.</t>
-  </si>
-  <si>
-    <t>the fraction of the sample that was diluted (for example if you split the sample 4 times that is 1/16th of the total sample so 16 is the value used)</t>
-  </si>
-  <si>
-    <t>volume calculated from net flowmeter in L</t>
-  </si>
-  <si>
-    <t>Term to encompass the conversion from particles to particles/mL - in this case the volume (in mL) the net sample is diluted into before passing it through the FlowCam</t>
+    <t>particles_perL</t>
+  </si>
+  <si>
+    <t>number of organisms per liter in the group where group is from data_provider_category_manual</t>
+  </si>
+  <si>
+    <t>cruise</t>
+  </si>
+  <si>
+    <t>cruise identifier</t>
+  </si>
+  <si>
+    <t>cells per Liter</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1690,6 +1731,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1735,7 +1781,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2042,37 +2090,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{212F2188-CDA4-45F0-9748-84A3C71A912B}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="3">
         <v>45884</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>359</v>
       </c>
@@ -2085,7 +2133,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
@@ -2098,7 +2146,7 @@
     <col min="10" max="10" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -2130,7 +2178,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2159,7 +2207,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2188,7 +2236,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2217,7 +2265,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2246,7 +2294,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2275,7 +2323,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2304,7 +2352,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2333,7 +2381,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.75">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2362,7 +2410,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15.75">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2391,7 +2439,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="15.75">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2420,7 +2468,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.75">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2449,7 +2497,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15.75">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2478,7 +2526,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15.75">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2507,7 +2555,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15.75">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2536,7 +2584,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.75">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2565,7 +2613,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15.75">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2594,7 +2642,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15.75">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2623,7 +2671,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15.75">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2652,7 +2700,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15.75">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2681,7 +2729,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15.75">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2710,7 +2758,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15.75">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2739,7 +2787,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15.75">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2768,7 +2816,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15.75">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -2797,7 +2845,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15.75">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2826,7 +2874,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15.75">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2855,7 +2903,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15.75">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2884,7 +2932,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15.75">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -2913,7 +2961,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15.75">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2942,7 +2990,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15.75">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2971,7 +3019,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15.75">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -3000,7 +3048,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15.75">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -3029,7 +3077,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="15.75">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -3058,7 +3106,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="15.75">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -3087,7 +3135,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="15.75">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3116,7 +3164,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="15.75">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -3145,7 +3193,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="15.75">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -3174,7 +3222,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="15.75">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -3203,7 +3251,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="15.75">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -3232,7 +3280,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="15.75">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -3261,7 +3309,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="15.75">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3290,7 +3338,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="15.75">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -3319,7 +3367,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="15.75">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -3348,7 +3396,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="15.75">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3377,7 +3425,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="15.75">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -3406,7 +3454,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="15.75">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3435,7 +3483,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="15.75">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -3464,7 +3512,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="15.75">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -3493,7 +3541,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="15.75">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3522,7 +3570,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="15.75">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -3551,7 +3599,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="15.75">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -3580,7 +3628,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="15.75">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -3609,7 +3657,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="15.75">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -3638,7 +3686,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15.75">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -3667,7 +3715,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="15.75">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -3696,7 +3744,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -3725,7 +3773,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -3754,7 +3802,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="15.75">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -3783,7 +3831,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="15.75">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -3812,7 +3860,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="15.75">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -3841,7 +3889,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="15.75">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -3870,7 +3918,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="15.75">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -3899,7 +3947,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="15.75">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -3928,7 +3976,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="15.75">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -3960,7 +4008,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="15.75">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -3997,7 +4045,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8991815-1D31-4593-9F80-5C6680CDDD79}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="70.5703125" customWidth="1"/>
@@ -4011,7 +4059,7 @@
     <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -4043,7 +4091,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>181</v>
       </c>
@@ -4072,7 +4120,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>184</v>
       </c>
@@ -4101,7 +4149,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>186</v>
       </c>
@@ -4130,7 +4178,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4159,7 +4207,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>190</v>
       </c>
@@ -4188,7 +4236,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>193</v>
       </c>
@@ -4217,7 +4265,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>195</v>
       </c>
@@ -4246,7 +4294,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>198</v>
       </c>
@@ -4275,7 +4323,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -4304,7 +4352,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>204</v>
       </c>
@@ -4333,7 +4381,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>206</v>
       </c>
@@ -4362,7 +4410,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -4391,7 +4439,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>210</v>
       </c>
@@ -4420,7 +4468,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>213</v>
       </c>
@@ -4457,14 +4505,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2697E4D0-01FA-4D17-8BBE-F5E7FE4EFC08}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="61.5703125" customWidth="1"/>
     <col min="3" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -4496,7 +4544,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>158</v>
       </c>
@@ -4525,7 +4573,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -4554,7 +4602,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>160</v>
       </c>
@@ -4583,7 +4631,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>161</v>
       </c>
@@ -4612,7 +4660,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -4644,7 +4692,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>287</v>
       </c>
@@ -4673,7 +4721,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>289</v>
       </c>
@@ -4705,7 +4753,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>291</v>
       </c>
@@ -4734,7 +4782,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -4766,7 +4814,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>293</v>
       </c>
@@ -4795,7 +4843,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>295</v>
       </c>
@@ -4824,7 +4872,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>298</v>
       </c>
@@ -4864,13 +4912,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7099CAE1-6CB4-4BAE-923C-2C4D2F549912}">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="66.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -4902,7 +4950,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>158</v>
       </c>
@@ -4931,7 +4979,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -4960,7 +5008,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>160</v>
       </c>
@@ -4989,7 +5037,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>161</v>
       </c>
@@ -5018,7 +5066,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -5050,7 +5098,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>240</v>
       </c>
@@ -5079,7 +5127,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>243</v>
       </c>
@@ -5108,7 +5156,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>245</v>
       </c>
@@ -5137,7 +5185,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>247</v>
       </c>
@@ -5166,7 +5214,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>249</v>
       </c>
@@ -5195,7 +5243,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>251</v>
       </c>
@@ -5224,7 +5272,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>253</v>
       </c>
@@ -5253,7 +5301,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>255</v>
       </c>
@@ -5282,7 +5330,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>257</v>
       </c>
@@ -5311,7 +5359,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>259</v>
       </c>
@@ -5340,7 +5388,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>261</v>
       </c>
@@ -5369,7 +5417,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>263</v>
       </c>
@@ -5398,7 +5446,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>265</v>
       </c>
@@ -5427,7 +5475,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>267</v>
       </c>
@@ -5456,7 +5504,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>269</v>
       </c>
@@ -5485,7 +5533,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>271</v>
       </c>
@@ -5514,7 +5562,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>272</v>
       </c>
@@ -5543,7 +5591,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>274</v>
       </c>
@@ -5572,7 +5620,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>275</v>
       </c>
@@ -5601,7 +5649,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>277</v>
       </c>
@@ -5630,7 +5678,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>279</v>
       </c>
@@ -5659,7 +5707,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>281</v>
       </c>
@@ -5688,7 +5736,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>283</v>
       </c>
@@ -5717,7 +5765,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>285</v>
       </c>
@@ -5754,7 +5802,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB974035-0AE0-4708-B122-4F86D23A7186}">
   <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -5768,7 +5816,7 @@
     <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -5800,7 +5848,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>158</v>
       </c>
@@ -5829,7 +5877,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -5858,7 +5906,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>160</v>
       </c>
@@ -5887,7 +5935,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>161</v>
       </c>
@@ -5916,7 +5964,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -5945,7 +5993,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -5977,7 +6025,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>163</v>
       </c>
@@ -6006,7 +6054,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6038,7 +6086,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>164</v>
       </c>
@@ -6067,7 +6115,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>165</v>
       </c>
@@ -6099,7 +6147,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>166</v>
       </c>
@@ -6128,7 +6176,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -6160,7 +6208,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>167</v>
       </c>
@@ -6189,7 +6237,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -6221,7 +6269,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>168</v>
       </c>
@@ -6250,7 +6298,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -6282,7 +6330,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>169</v>
       </c>
@@ -6311,7 +6359,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>170</v>
       </c>
@@ -6343,7 +6391,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>171</v>
       </c>
@@ -6372,7 +6420,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -6404,7 +6452,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>172</v>
       </c>
@@ -6433,7 +6481,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -6465,7 +6513,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>173</v>
       </c>
@@ -6494,7 +6542,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -6526,7 +6574,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>174</v>
       </c>
@@ -6555,7 +6603,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -6587,7 +6635,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>175</v>
       </c>
@@ -6616,7 +6664,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -6648,7 +6696,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>176</v>
       </c>
@@ -6677,7 +6725,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -6709,7 +6757,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -6738,7 +6786,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -6770,7 +6818,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>178</v>
       </c>
@@ -6799,7 +6847,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -6831,7 +6879,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>179</v>
       </c>
@@ -6860,7 +6908,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>47</v>
       </c>
@@ -6892,7 +6940,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>180</v>
       </c>
@@ -6930,7 +6978,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41A31BB-44F9-4FF4-A103-F42535BD8AD4}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.28515625" customWidth="1"/>
     <col min="2" max="2" width="56.7109375" customWidth="1"/>
@@ -6944,7 +6992,7 @@
     <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -6976,7 +7024,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>299</v>
       </c>
@@ -7005,7 +7053,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -7034,7 +7082,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>160</v>
       </c>
@@ -7063,7 +7111,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>300</v>
       </c>
@@ -7092,7 +7140,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>302</v>
       </c>
@@ -7124,7 +7172,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>303</v>
       </c>
@@ -7153,7 +7201,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>306</v>
       </c>
@@ -7182,7 +7230,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>308</v>
       </c>
@@ -7211,7 +7259,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>311</v>
       </c>
@@ -7240,7 +7288,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>313</v>
       </c>
@@ -7269,7 +7317,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -7298,7 +7346,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>317</v>
       </c>
@@ -7327,7 +7375,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>319</v>
       </c>
@@ -7356,7 +7404,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>321</v>
       </c>
@@ -7385,7 +7433,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>323</v>
       </c>
@@ -7417,7 +7465,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>324</v>
       </c>
@@ -7453,12 +7501,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F9E499-8F3B-4962-B041-C7E33D10A5CD}">
-  <dimension ref="A1:J71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J73"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="171.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="112.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -7468,7 +7516,7 @@
     <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -7500,13 +7548,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>397</v>
       </c>
       <c r="B2" t="s">
         <v>398</v>
       </c>
+      <c r="C2" t="s">
+        <v>387</v>
+      </c>
       <c r="D2" t="s">
         <v>399</v>
       </c>
@@ -7526,64 +7577,73 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D3" t="s">
         <v>401</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
         <v>402</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
         <v>403</v>
       </c>
-      <c r="E3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
         <v>404</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>405</v>
       </c>
-      <c r="D4" t="s">
-        <v>403</v>
-      </c>
-      <c r="E4" t="s">
-        <v>150</v>
-      </c>
-      <c r="F4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B5" t="s">
-        <v>407</v>
+      <c r="C5" t="s">
+        <v>387</v>
       </c>
       <c r="D5" t="s">
         <v>192</v>
@@ -7604,15 +7664,2140 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B6" t="s">
+        <v>407</v>
+      </c>
+      <c r="C6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D6" t="s">
         <v>408</v>
       </c>
+      <c r="E6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D7" t="s">
+        <v>408</v>
+      </c>
+      <c r="E7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>550</v>
+      </c>
+      <c r="B8" t="s">
+        <v>551</v>
+      </c>
+      <c r="C8" t="s">
+        <v>387</v>
+      </c>
+      <c r="D8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" t="s">
+        <v>387</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C9" t="s">
+        <v>387</v>
+      </c>
+      <c r="D9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>413</v>
+      </c>
+      <c r="B10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C10" t="s">
+        <v>387</v>
+      </c>
+      <c r="D10" t="s">
+        <v>408</v>
+      </c>
+      <c r="E10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>415</v>
+      </c>
+      <c r="B11" t="s">
+        <v>416</v>
+      </c>
+      <c r="C11" t="s">
+        <v>387</v>
+      </c>
+      <c r="D11" t="s">
+        <v>417</v>
+      </c>
+      <c r="E11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G11" t="s">
+        <v>197</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>397</v>
+      </c>
+      <c r="B12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C12" t="s">
+        <v>387</v>
+      </c>
+      <c r="D12" t="s">
+        <v>399</v>
+      </c>
+      <c r="E12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" t="s">
+        <v>197</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>418</v>
+      </c>
+      <c r="B13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" t="s">
+        <v>387</v>
+      </c>
+      <c r="D13" t="s">
+        <v>419</v>
+      </c>
+      <c r="E13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>420</v>
+      </c>
+      <c r="B14" t="s">
+        <v>421</v>
+      </c>
+      <c r="C14" t="s">
+        <v>387</v>
+      </c>
+      <c r="D14" t="s">
+        <v>408</v>
+      </c>
+      <c r="E14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" t="s">
+        <v>197</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>422</v>
+      </c>
+      <c r="B15" t="s">
+        <v>519</v>
+      </c>
+      <c r="C15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D15" t="s">
+        <v>423</v>
+      </c>
+      <c r="E15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>424</v>
+      </c>
+      <c r="B16" t="s">
+        <v>520</v>
+      </c>
+      <c r="C16" t="s">
+        <v>518</v>
+      </c>
+      <c r="D16" t="s">
+        <v>423</v>
+      </c>
+      <c r="E16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" t="s">
+        <v>197</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>425</v>
+      </c>
+      <c r="B17" t="s">
+        <v>521</v>
+      </c>
+      <c r="C17" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" t="s">
+        <v>423</v>
+      </c>
+      <c r="E17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" t="s">
+        <v>150</v>
+      </c>
+      <c r="G17" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>426</v>
+      </c>
+      <c r="B18" t="s">
+        <v>522</v>
+      </c>
+      <c r="C18" t="s">
+        <v>518</v>
+      </c>
+      <c r="D18" t="s">
+        <v>423</v>
+      </c>
+      <c r="E18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" t="s">
+        <v>197</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>427</v>
+      </c>
+      <c r="B19" t="s">
+        <v>523</v>
+      </c>
+      <c r="C19" t="s">
+        <v>518</v>
+      </c>
+      <c r="D19" t="s">
+        <v>423</v>
+      </c>
+      <c r="E19" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" t="s">
+        <v>197</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>428</v>
+      </c>
+      <c r="B20" t="s">
+        <v>524</v>
+      </c>
+      <c r="C20" t="s">
+        <v>518</v>
+      </c>
+      <c r="D20" t="s">
+        <v>423</v>
+      </c>
+      <c r="E20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" t="s">
+        <v>197</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>429</v>
+      </c>
+      <c r="B21" t="s">
+        <v>525</v>
+      </c>
+      <c r="C21" t="s">
+        <v>518</v>
+      </c>
+      <c r="D21" t="s">
+        <v>423</v>
+      </c>
+      <c r="E21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>430</v>
+      </c>
+      <c r="B22" t="s">
+        <v>526</v>
+      </c>
+      <c r="C22" t="s">
+        <v>518</v>
+      </c>
+      <c r="D22" t="s">
+        <v>423</v>
+      </c>
+      <c r="E22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>431</v>
+      </c>
+      <c r="B23" t="s">
+        <v>432</v>
+      </c>
+      <c r="C23" t="s">
+        <v>518</v>
+      </c>
+      <c r="D23" t="s">
+        <v>423</v>
+      </c>
+      <c r="E23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" t="s">
+        <v>197</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>433</v>
+      </c>
+      <c r="B24" t="s">
+        <v>527</v>
+      </c>
+      <c r="C24" t="s">
+        <v>518</v>
+      </c>
+      <c r="D24" t="s">
+        <v>423</v>
+      </c>
+      <c r="E24" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" t="s">
+        <v>197</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>434</v>
+      </c>
+      <c r="B25" t="s">
+        <v>528</v>
+      </c>
+      <c r="C25" t="s">
+        <v>518</v>
+      </c>
+      <c r="D25" t="s">
+        <v>423</v>
+      </c>
+      <c r="E25" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" t="s">
+        <v>197</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>435</v>
+      </c>
+      <c r="B26" t="s">
+        <v>529</v>
+      </c>
+      <c r="C26" t="s">
+        <v>518</v>
+      </c>
+      <c r="D26" t="s">
+        <v>423</v>
+      </c>
+      <c r="E26" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" t="s">
+        <v>197</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>436</v>
+      </c>
+      <c r="B27" t="s">
+        <v>530</v>
+      </c>
+      <c r="C27" t="s">
+        <v>518</v>
+      </c>
+      <c r="D27" t="s">
+        <v>423</v>
+      </c>
+      <c r="E27" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" t="s">
+        <v>197</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>437</v>
+      </c>
+      <c r="B28" t="s">
+        <v>531</v>
+      </c>
+      <c r="C28" t="s">
+        <v>518</v>
+      </c>
+      <c r="D28" t="s">
+        <v>423</v>
+      </c>
+      <c r="E28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" t="s">
+        <v>150</v>
+      </c>
+      <c r="G28" t="s">
+        <v>197</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>438</v>
+      </c>
+      <c r="B29" t="s">
+        <v>532</v>
+      </c>
+      <c r="C29" t="s">
+        <v>518</v>
+      </c>
+      <c r="D29" t="s">
+        <v>423</v>
+      </c>
+      <c r="E29" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>439</v>
+      </c>
+      <c r="B30" t="s">
+        <v>533</v>
+      </c>
+      <c r="C30" t="s">
+        <v>518</v>
+      </c>
+      <c r="D30" t="s">
+        <v>423</v>
+      </c>
+      <c r="E30" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>440</v>
+      </c>
+      <c r="B31" t="s">
+        <v>534</v>
+      </c>
+      <c r="C31" t="s">
+        <v>518</v>
+      </c>
+      <c r="D31" t="s">
+        <v>423</v>
+      </c>
+      <c r="E31" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" t="s">
+        <v>197</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>441</v>
+      </c>
+      <c r="B32" t="s">
+        <v>535</v>
+      </c>
+      <c r="C32" t="s">
+        <v>518</v>
+      </c>
+      <c r="D32" t="s">
+        <v>423</v>
+      </c>
+      <c r="E32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" t="s">
+        <v>197</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>442</v>
+      </c>
+      <c r="B33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C33" t="s">
+        <v>518</v>
+      </c>
+      <c r="D33" t="s">
+        <v>423</v>
+      </c>
+      <c r="E33" t="s">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" t="s">
+        <v>197</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>443</v>
+      </c>
+      <c r="B34" t="s">
+        <v>537</v>
+      </c>
+      <c r="C34" t="s">
+        <v>518</v>
+      </c>
+      <c r="D34" t="s">
+        <v>423</v>
+      </c>
+      <c r="E34" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>444</v>
+      </c>
+      <c r="B35" t="s">
+        <v>538</v>
+      </c>
+      <c r="C35" t="s">
+        <v>518</v>
+      </c>
+      <c r="D35" t="s">
+        <v>423</v>
+      </c>
+      <c r="E35" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" t="s">
+        <v>150</v>
+      </c>
+      <c r="G35" t="s">
+        <v>197</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>445</v>
+      </c>
+      <c r="B36" t="s">
+        <v>446</v>
+      </c>
+      <c r="C36" t="s">
+        <v>518</v>
+      </c>
+      <c r="D36" t="s">
+        <v>423</v>
+      </c>
+      <c r="E36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" t="s">
+        <v>150</v>
+      </c>
+      <c r="G36" t="s">
+        <v>197</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>447</v>
+      </c>
+      <c r="B37" t="s">
+        <v>448</v>
+      </c>
+      <c r="C37" t="s">
+        <v>518</v>
+      </c>
+      <c r="D37" t="s">
+        <v>408</v>
+      </c>
+      <c r="E37" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>449</v>
+      </c>
+      <c r="B38" t="s">
+        <v>450</v>
+      </c>
+      <c r="C38" t="s">
+        <v>518</v>
+      </c>
+      <c r="D38" t="s">
+        <v>408</v>
+      </c>
+      <c r="E38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" t="s">
+        <v>150</v>
+      </c>
+      <c r="G38" t="s">
+        <v>197</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>451</v>
+      </c>
+      <c r="B39" t="s">
+        <v>539</v>
+      </c>
+      <c r="C39" t="s">
+        <v>518</v>
+      </c>
+      <c r="D39" t="s">
+        <v>423</v>
+      </c>
+      <c r="E39" t="s">
+        <v>150</v>
+      </c>
+      <c r="F39" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" t="s">
+        <v>197</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>452</v>
+      </c>
+      <c r="B40" t="s">
+        <v>453</v>
+      </c>
+      <c r="C40" t="s">
+        <v>518</v>
+      </c>
+      <c r="D40" t="s">
+        <v>423</v>
+      </c>
+      <c r="E40" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40" t="s">
+        <v>197</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>454</v>
+      </c>
+      <c r="B41" t="s">
+        <v>455</v>
+      </c>
+      <c r="C41" t="s">
+        <v>518</v>
+      </c>
+      <c r="D41" t="s">
+        <v>408</v>
+      </c>
+      <c r="E41" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" t="s">
+        <v>150</v>
+      </c>
+      <c r="G41" t="s">
+        <v>197</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>456</v>
+      </c>
+      <c r="B42" t="s">
+        <v>457</v>
+      </c>
+      <c r="C42" t="s">
+        <v>518</v>
+      </c>
+      <c r="D42" t="s">
+        <v>423</v>
+      </c>
+      <c r="E42" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" t="s">
+        <v>150</v>
+      </c>
+      <c r="G42" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>458</v>
+      </c>
+      <c r="B43" t="s">
+        <v>459</v>
+      </c>
+      <c r="C43" t="s">
+        <v>518</v>
+      </c>
+      <c r="D43" t="s">
+        <v>408</v>
+      </c>
+      <c r="E43" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" t="s">
+        <v>150</v>
+      </c>
+      <c r="G43" t="s">
+        <v>197</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>460</v>
+      </c>
+      <c r="B44" t="s">
+        <v>461</v>
+      </c>
+      <c r="C44" t="s">
+        <v>518</v>
+      </c>
+      <c r="D44" t="s">
+        <v>423</v>
+      </c>
+      <c r="E44" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" t="s">
+        <v>150</v>
+      </c>
+      <c r="G44" t="s">
+        <v>197</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>462</v>
+      </c>
+      <c r="B45" t="s">
+        <v>463</v>
+      </c>
+      <c r="C45" t="s">
+        <v>518</v>
+      </c>
+      <c r="D45" t="s">
+        <v>408</v>
+      </c>
+      <c r="E45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" t="s">
+        <v>150</v>
+      </c>
+      <c r="G45" t="s">
+        <v>197</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>464</v>
+      </c>
+      <c r="B46" t="s">
+        <v>465</v>
+      </c>
+      <c r="C46" t="s">
+        <v>518</v>
+      </c>
+      <c r="D46" t="s">
+        <v>423</v>
+      </c>
+      <c r="E46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" t="s">
+        <v>150</v>
+      </c>
+      <c r="G46" t="s">
+        <v>197</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>466</v>
+      </c>
+      <c r="B47" t="s">
+        <v>467</v>
+      </c>
+      <c r="C47" t="s">
+        <v>518</v>
+      </c>
+      <c r="D47" t="s">
+        <v>423</v>
+      </c>
+      <c r="E47" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" t="s">
+        <v>197</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>468</v>
+      </c>
+      <c r="B48" t="s">
+        <v>469</v>
+      </c>
+      <c r="C48" t="s">
+        <v>518</v>
+      </c>
+      <c r="D48" t="s">
+        <v>408</v>
+      </c>
+      <c r="E48" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" t="s">
+        <v>150</v>
+      </c>
+      <c r="G48" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>470</v>
+      </c>
+      <c r="B49" t="s">
+        <v>471</v>
+      </c>
+      <c r="C49" t="s">
+        <v>518</v>
+      </c>
+      <c r="D49" t="s">
+        <v>408</v>
+      </c>
+      <c r="E49" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" t="s">
+        <v>150</v>
+      </c>
+      <c r="G49" t="s">
+        <v>197</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>472</v>
+      </c>
+      <c r="B50" t="s">
+        <v>540</v>
+      </c>
+      <c r="C50" t="s">
+        <v>518</v>
+      </c>
+      <c r="D50" t="s">
+        <v>423</v>
+      </c>
+      <c r="E50" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" t="s">
+        <v>197</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>473</v>
+      </c>
+      <c r="B51" t="s">
+        <v>541</v>
+      </c>
+      <c r="C51" t="s">
+        <v>518</v>
+      </c>
+      <c r="D51" t="s">
+        <v>423</v>
+      </c>
+      <c r="E51" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" t="s">
+        <v>197</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>474</v>
+      </c>
+      <c r="B52" t="s">
+        <v>542</v>
+      </c>
+      <c r="C52" t="s">
+        <v>518</v>
+      </c>
+      <c r="D52" t="s">
+        <v>423</v>
+      </c>
+      <c r="E52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F52" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" t="s">
+        <v>197</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>475</v>
+      </c>
+      <c r="B53" t="s">
+        <v>476</v>
+      </c>
+      <c r="C53" t="s">
+        <v>518</v>
+      </c>
+      <c r="D53" t="s">
+        <v>423</v>
+      </c>
+      <c r="E53" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" t="s">
+        <v>197</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>477</v>
+      </c>
+      <c r="B54" t="s">
+        <v>543</v>
+      </c>
+      <c r="C54" t="s">
+        <v>518</v>
+      </c>
+      <c r="D54" t="s">
+        <v>423</v>
+      </c>
+      <c r="E54" t="s">
+        <v>150</v>
+      </c>
+      <c r="F54" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" t="s">
+        <v>197</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>478</v>
+      </c>
+      <c r="B55" t="s">
+        <v>544</v>
+      </c>
+      <c r="C55" t="s">
+        <v>518</v>
+      </c>
+      <c r="D55" t="s">
+        <v>423</v>
+      </c>
+      <c r="E55" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" t="s">
+        <v>150</v>
+      </c>
+      <c r="G55" t="s">
+        <v>197</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>479</v>
+      </c>
+      <c r="B56" t="s">
+        <v>507</v>
+      </c>
+      <c r="C56" t="s">
+        <v>517</v>
+      </c>
+      <c r="D56" t="s">
+        <v>408</v>
+      </c>
+      <c r="E56" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" t="s">
+        <v>150</v>
+      </c>
+      <c r="G56" t="s">
+        <v>197</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>480</v>
+      </c>
+      <c r="B57" t="s">
+        <v>511</v>
+      </c>
+      <c r="C57" t="s">
+        <v>517</v>
+      </c>
+      <c r="D57" t="s">
+        <v>408</v>
+      </c>
+      <c r="E57" t="s">
+        <v>150</v>
+      </c>
+      <c r="F57" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" t="s">
+        <v>197</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>481</v>
+      </c>
+      <c r="B58" t="s">
+        <v>506</v>
+      </c>
+      <c r="C58" t="s">
+        <v>517</v>
+      </c>
+      <c r="D58" t="s">
+        <v>408</v>
+      </c>
+      <c r="E58" t="s">
+        <v>150</v>
+      </c>
+      <c r="F58" t="s">
+        <v>150</v>
+      </c>
+      <c r="G58" t="s">
+        <v>197</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>482</v>
+      </c>
+      <c r="B59" t="s">
+        <v>483</v>
+      </c>
+      <c r="C59" t="s">
+        <v>517</v>
+      </c>
+      <c r="D59" t="s">
+        <v>419</v>
+      </c>
+      <c r="E59" t="s">
+        <v>150</v>
+      </c>
+      <c r="F59" t="s">
+        <v>150</v>
+      </c>
+      <c r="G59" t="s">
+        <v>197</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>484</v>
+      </c>
+      <c r="B60" t="s">
+        <v>485</v>
+      </c>
+      <c r="C60" t="s">
+        <v>517</v>
+      </c>
+      <c r="D60" t="s">
+        <v>408</v>
+      </c>
+      <c r="E60" t="s">
+        <v>150</v>
+      </c>
+      <c r="F60" t="s">
+        <v>150</v>
+      </c>
+      <c r="G60" t="s">
+        <v>197</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>486</v>
+      </c>
+      <c r="B61" t="s">
+        <v>487</v>
+      </c>
+      <c r="C61" t="s">
+        <v>517</v>
+      </c>
+      <c r="D61" t="s">
+        <v>408</v>
+      </c>
+      <c r="E61" t="s">
+        <v>150</v>
+      </c>
+      <c r="F61" t="s">
+        <v>150</v>
+      </c>
+      <c r="G61" t="s">
+        <v>197</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>488</v>
+      </c>
+      <c r="B62" t="s">
+        <v>513</v>
+      </c>
+      <c r="C62" t="s">
+        <v>517</v>
+      </c>
+      <c r="D62" t="s">
+        <v>408</v>
+      </c>
+      <c r="E62" t="s">
+        <v>150</v>
+      </c>
+      <c r="F62" t="s">
+        <v>150</v>
+      </c>
+      <c r="G62" t="s">
+        <v>197</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>489</v>
+      </c>
+      <c r="B63" t="s">
+        <v>512</v>
+      </c>
+      <c r="C63" t="s">
+        <v>517</v>
+      </c>
+      <c r="D63" t="s">
+        <v>490</v>
+      </c>
+      <c r="E63" t="s">
+        <v>150</v>
+      </c>
+      <c r="F63" t="s">
+        <v>150</v>
+      </c>
+      <c r="G63" t="s">
+        <v>197</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>491</v>
+      </c>
+      <c r="B64" t="s">
+        <v>508</v>
+      </c>
+      <c r="C64" t="s">
+        <v>517</v>
+      </c>
+      <c r="D64" t="s">
+        <v>492</v>
+      </c>
+      <c r="E64" t="s">
+        <v>150</v>
+      </c>
+      <c r="F64" t="s">
+        <v>150</v>
+      </c>
+      <c r="G64" t="s">
+        <v>197</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>493</v>
+      </c>
+      <c r="B65" t="s">
+        <v>509</v>
+      </c>
+      <c r="C65" t="s">
+        <v>517</v>
+      </c>
+      <c r="D65" t="s">
+        <v>492</v>
+      </c>
+      <c r="E65" t="s">
+        <v>150</v>
+      </c>
+      <c r="F65" t="s">
+        <v>150</v>
+      </c>
+      <c r="G65" t="s">
+        <v>197</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>494</v>
+      </c>
+      <c r="B66" t="s">
+        <v>510</v>
+      </c>
+      <c r="C66" t="s">
+        <v>517</v>
+      </c>
+      <c r="D66" t="s">
+        <v>492</v>
+      </c>
+      <c r="E66" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" t="s">
+        <v>150</v>
+      </c>
+      <c r="G66" t="s">
+        <v>197</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>495</v>
+      </c>
+      <c r="B67" t="s">
+        <v>496</v>
+      </c>
+      <c r="C67" t="s">
+        <v>517</v>
+      </c>
+      <c r="D67" t="s">
+        <v>497</v>
+      </c>
+      <c r="E67" t="s">
+        <v>150</v>
+      </c>
+      <c r="F67" t="s">
+        <v>150</v>
+      </c>
+      <c r="G67" t="s">
+        <v>197</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>498</v>
+      </c>
+      <c r="B68" t="s">
+        <v>499</v>
+      </c>
+      <c r="C68" t="s">
+        <v>517</v>
+      </c>
+      <c r="D68" t="s">
+        <v>497</v>
+      </c>
+      <c r="E68" t="s">
+        <v>150</v>
+      </c>
+      <c r="F68" t="s">
+        <v>150</v>
+      </c>
+      <c r="G68" t="s">
+        <v>197</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>500</v>
+      </c>
+      <c r="B69" t="s">
+        <v>515</v>
+      </c>
+      <c r="C69" t="s">
+        <v>517</v>
+      </c>
+      <c r="D69" t="s">
+        <v>419</v>
+      </c>
+      <c r="E69" t="s">
+        <v>150</v>
+      </c>
+      <c r="F69" t="s">
+        <v>150</v>
+      </c>
+      <c r="G69" t="s">
+        <v>197</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>501</v>
+      </c>
+      <c r="B70" t="s">
+        <v>514</v>
+      </c>
+      <c r="C70" t="s">
+        <v>517</v>
+      </c>
+      <c r="D70" t="s">
+        <v>408</v>
+      </c>
+      <c r="E70" t="s">
+        <v>150</v>
+      </c>
+      <c r="F70" t="s">
+        <v>150</v>
+      </c>
+      <c r="G70" t="s">
+        <v>197</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>502</v>
+      </c>
+      <c r="B71" t="s">
+        <v>516</v>
+      </c>
+      <c r="C71" t="s">
+        <v>517</v>
+      </c>
+      <c r="D71" t="s">
+        <v>408</v>
+      </c>
+      <c r="E71" t="s">
+        <v>150</v>
+      </c>
+      <c r="F71" t="s">
+        <v>150</v>
+      </c>
+      <c r="G71" t="s">
+        <v>197</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>503</v>
+      </c>
+      <c r="B72" t="s">
+        <v>545</v>
+      </c>
+      <c r="C72" t="s">
+        <v>517</v>
+      </c>
+      <c r="D72" t="s">
+        <v>505</v>
+      </c>
+      <c r="E72" t="s">
+        <v>150</v>
+      </c>
+      <c r="F72" t="s">
+        <v>150</v>
+      </c>
+      <c r="G72" t="s">
+        <v>197</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="B73" t="s">
+        <v>549</v>
+      </c>
+      <c r="C73" t="s">
+        <v>517</v>
+      </c>
+      <c r="D73" t="s">
+        <v>552</v>
+      </c>
+      <c r="E73" t="s">
+        <v>150</v>
+      </c>
+      <c r="F73" t="s">
+        <v>150</v>
+      </c>
+      <c r="G73" t="s">
+        <v>197</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41309215-EB4C-48B3-A3D7-89B6FA6A2DA4}">
+  <dimension ref="A1:I68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="112.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D4" t="s">
+        <v>408</v>
+      </c>
+      <c r="E4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>411</v>
+      </c>
+      <c r="B5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5" t="s">
+        <v>197</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>413</v>
+      </c>
       <c r="B6" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E6" t="s">
         <v>150</v>
@@ -7630,15 +9815,15 @@
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B7" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D7" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="E7" t="s">
         <v>150</v>
@@ -7656,15 +9841,15 @@
         <v>400</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="B8" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="D8" t="s">
-        <v>192</v>
+        <v>399</v>
       </c>
       <c r="E8" t="s">
         <v>150</v>
@@ -7682,15 +9867,15 @@
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B9" t="s">
-        <v>416</v>
+        <v>211</v>
       </c>
       <c r="D9" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="E9" t="s">
         <v>150</v>
@@ -7708,15 +9893,15 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B10" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D10" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="E10" t="s">
         <v>150</v>
@@ -7734,15 +9919,18 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="B11" t="s">
-        <v>398</v>
+        <v>519</v>
+      </c>
+      <c r="C11" t="s">
+        <v>518</v>
       </c>
       <c r="D11" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="E11" t="s">
         <v>150</v>
@@ -7754,21 +9942,24 @@
         <v>197</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>520</v>
+      </c>
+      <c r="C12" t="s">
+        <v>518</v>
       </c>
       <c r="D12" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E12" t="s">
         <v>150</v>
@@ -7780,22 +9971,25 @@
         <v>197</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B13" t="s">
+        <v>521</v>
+      </c>
+      <c r="C13" t="s">
+        <v>518</v>
+      </c>
+      <c r="D13" t="s">
         <v>423</v>
       </c>
-      <c r="D13" t="s">
-        <v>410</v>
-      </c>
       <c r="E13" t="s">
         <v>150</v>
       </c>
@@ -7806,21 +10000,24 @@
         <v>197</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B14" t="s">
-        <v>425</v>
+        <v>522</v>
+      </c>
+      <c r="C14" t="s">
+        <v>518</v>
       </c>
       <c r="D14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E14" t="s">
         <v>150</v>
@@ -7838,1029 +10035,1101 @@
         <v>400</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>427</v>
       </c>
       <c r="B15" t="s">
+        <v>523</v>
+      </c>
+      <c r="C15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D15" t="s">
+        <v>423</v>
+      </c>
+      <c r="E15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
         <v>428</v>
       </c>
-      <c r="D15" t="s">
-        <v>426</v>
-      </c>
-      <c r="E15" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" t="s">
-        <v>150</v>
-      </c>
-      <c r="G15" t="s">
-        <v>197</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>524</v>
+      </c>
+      <c r="C16" t="s">
+        <v>518</v>
+      </c>
+      <c r="D16" t="s">
+        <v>423</v>
+      </c>
+      <c r="E16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" t="s">
+        <v>197</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
         <v>429</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
+        <v>525</v>
+      </c>
+      <c r="C17" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" t="s">
+        <v>423</v>
+      </c>
+      <c r="E17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" t="s">
+        <v>150</v>
+      </c>
+      <c r="G17" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
         <v>430</v>
       </c>
-      <c r="D16" t="s">
-        <v>426</v>
-      </c>
-      <c r="E16" t="s">
-        <v>150</v>
-      </c>
-      <c r="F16" t="s">
-        <v>150</v>
-      </c>
-      <c r="G16" t="s">
-        <v>197</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
+        <v>526</v>
+      </c>
+      <c r="C18" t="s">
+        <v>518</v>
+      </c>
+      <c r="D18" t="s">
+        <v>423</v>
+      </c>
+      <c r="E18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" t="s">
+        <v>197</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
         <v>431</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" t="s">
         <v>432</v>
       </c>
-      <c r="D17" t="s">
-        <v>426</v>
-      </c>
-      <c r="E17" t="s">
-        <v>150</v>
-      </c>
-      <c r="F17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G17" t="s">
-        <v>197</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="D19" t="s">
+        <v>423</v>
+      </c>
+      <c r="E19" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" t="s">
+        <v>197</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
         <v>433</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" t="s">
+        <v>527</v>
+      </c>
+      <c r="C20" t="s">
+        <v>518</v>
+      </c>
+      <c r="D20" t="s">
+        <v>423</v>
+      </c>
+      <c r="E20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" t="s">
+        <v>197</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
         <v>434</v>
       </c>
-      <c r="D18" t="s">
-        <v>426</v>
-      </c>
-      <c r="E18" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G18" t="s">
-        <v>197</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B21" t="s">
+        <v>528</v>
+      </c>
+      <c r="C21" t="s">
+        <v>518</v>
+      </c>
+      <c r="D21" t="s">
+        <v>423</v>
+      </c>
+      <c r="E21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
         <v>435</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B22" t="s">
+        <v>529</v>
+      </c>
+      <c r="C22" t="s">
+        <v>518</v>
+      </c>
+      <c r="D22" t="s">
+        <v>423</v>
+      </c>
+      <c r="E22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
         <v>436</v>
       </c>
-      <c r="D19" t="s">
-        <v>426</v>
-      </c>
-      <c r="E19" t="s">
-        <v>150</v>
-      </c>
-      <c r="F19" t="s">
-        <v>150</v>
-      </c>
-      <c r="G19" t="s">
-        <v>197</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B23" t="s">
+        <v>530</v>
+      </c>
+      <c r="C23" t="s">
+        <v>518</v>
+      </c>
+      <c r="D23" t="s">
+        <v>423</v>
+      </c>
+      <c r="E23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" t="s">
+        <v>197</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
         <v>437</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B24" t="s">
+        <v>531</v>
+      </c>
+      <c r="C24" t="s">
+        <v>518</v>
+      </c>
+      <c r="D24" t="s">
+        <v>423</v>
+      </c>
+      <c r="E24" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" t="s">
+        <v>197</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
         <v>438</v>
       </c>
-      <c r="D20" t="s">
-        <v>426</v>
-      </c>
-      <c r="E20" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" t="s">
-        <v>150</v>
-      </c>
-      <c r="G20" t="s">
-        <v>197</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B25" t="s">
+        <v>532</v>
+      </c>
+      <c r="C25" t="s">
+        <v>518</v>
+      </c>
+      <c r="D25" t="s">
+        <v>423</v>
+      </c>
+      <c r="E25" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" t="s">
+        <v>197</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
         <v>439</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B26" t="s">
+        <v>533</v>
+      </c>
+      <c r="C26" t="s">
+        <v>518</v>
+      </c>
+      <c r="D26" t="s">
+        <v>423</v>
+      </c>
+      <c r="E26" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" t="s">
+        <v>197</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
         <v>440</v>
       </c>
-      <c r="D21" t="s">
-        <v>426</v>
-      </c>
-      <c r="E21" t="s">
-        <v>150</v>
-      </c>
-      <c r="F21" t="s">
-        <v>150</v>
-      </c>
-      <c r="G21" t="s">
-        <v>197</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B27" t="s">
+        <v>534</v>
+      </c>
+      <c r="C27" t="s">
+        <v>518</v>
+      </c>
+      <c r="D27" t="s">
+        <v>423</v>
+      </c>
+      <c r="E27" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" t="s">
+        <v>197</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
         <v>441</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B28" t="s">
+        <v>535</v>
+      </c>
+      <c r="C28" t="s">
+        <v>518</v>
+      </c>
+      <c r="D28" t="s">
+        <v>423</v>
+      </c>
+      <c r="E28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" t="s">
+        <v>150</v>
+      </c>
+      <c r="G28" t="s">
+        <v>197</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
         <v>442</v>
       </c>
-      <c r="D22" t="s">
-        <v>426</v>
-      </c>
-      <c r="E22" t="s">
-        <v>150</v>
-      </c>
-      <c r="F22" t="s">
-        <v>150</v>
-      </c>
-      <c r="G22" t="s">
-        <v>197</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B29" t="s">
+        <v>536</v>
+      </c>
+      <c r="C29" t="s">
+        <v>518</v>
+      </c>
+      <c r="D29" t="s">
+        <v>423</v>
+      </c>
+      <c r="E29" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
         <v>443</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B30" t="s">
+        <v>537</v>
+      </c>
+      <c r="C30" t="s">
+        <v>518</v>
+      </c>
+      <c r="D30" t="s">
+        <v>423</v>
+      </c>
+      <c r="E30" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
         <v>444</v>
       </c>
-      <c r="D23" t="s">
-        <v>426</v>
-      </c>
-      <c r="E23" t="s">
-        <v>150</v>
-      </c>
-      <c r="F23" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23" t="s">
-        <v>197</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B31" t="s">
+        <v>538</v>
+      </c>
+      <c r="C31" t="s">
+        <v>518</v>
+      </c>
+      <c r="D31" t="s">
+        <v>423</v>
+      </c>
+      <c r="E31" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" t="s">
+        <v>197</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
         <v>445</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B32" t="s">
         <v>446</v>
       </c>
-      <c r="D24" t="s">
-        <v>426</v>
-      </c>
-      <c r="E24" t="s">
-        <v>150</v>
-      </c>
-      <c r="F24" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" t="s">
-        <v>197</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="D32" t="s">
+        <v>423</v>
+      </c>
+      <c r="E32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" t="s">
+        <v>197</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
         <v>447</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B33" t="s">
         <v>448</v>
       </c>
-      <c r="D25" t="s">
-        <v>426</v>
-      </c>
-      <c r="E25" t="s">
-        <v>150</v>
-      </c>
-      <c r="F25" t="s">
-        <v>150</v>
-      </c>
-      <c r="G25" t="s">
-        <v>197</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="D33" t="s">
+        <v>408</v>
+      </c>
+      <c r="E33" t="s">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" t="s">
+        <v>197</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
         <v>449</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B34" t="s">
         <v>450</v>
       </c>
-      <c r="D26" t="s">
-        <v>426</v>
-      </c>
-      <c r="E26" t="s">
-        <v>150</v>
-      </c>
-      <c r="F26" t="s">
-        <v>150</v>
-      </c>
-      <c r="G26" t="s">
-        <v>197</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="D34" t="s">
+        <v>408</v>
+      </c>
+      <c r="E34" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
         <v>451</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B35" t="s">
+        <v>539</v>
+      </c>
+      <c r="C35" t="s">
+        <v>518</v>
+      </c>
+      <c r="D35" t="s">
+        <v>423</v>
+      </c>
+      <c r="E35" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" t="s">
+        <v>150</v>
+      </c>
+      <c r="G35" t="s">
+        <v>197</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
         <v>452</v>
       </c>
-      <c r="D27" t="s">
-        <v>426</v>
-      </c>
-      <c r="E27" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" t="s">
-        <v>150</v>
-      </c>
-      <c r="G27" t="s">
-        <v>197</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B36" t="s">
         <v>453</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D36" t="s">
+        <v>423</v>
+      </c>
+      <c r="E36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" t="s">
+        <v>150</v>
+      </c>
+      <c r="G36" t="s">
+        <v>197</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
         <v>454</v>
       </c>
-      <c r="D28" t="s">
-        <v>426</v>
-      </c>
-      <c r="E28" t="s">
-        <v>150</v>
-      </c>
-      <c r="F28" t="s">
-        <v>150</v>
-      </c>
-      <c r="G28" t="s">
-        <v>197</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B37" t="s">
         <v>455</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D37" t="s">
+        <v>408</v>
+      </c>
+      <c r="E37" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
         <v>456</v>
       </c>
-      <c r="D29" t="s">
-        <v>426</v>
-      </c>
-      <c r="E29" t="s">
-        <v>150</v>
-      </c>
-      <c r="F29" t="s">
-        <v>150</v>
-      </c>
-      <c r="G29" t="s">
-        <v>197</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B38" t="s">
         <v>457</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D38" t="s">
+        <v>423</v>
+      </c>
+      <c r="E38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" t="s">
+        <v>150</v>
+      </c>
+      <c r="G38" t="s">
+        <v>197</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
         <v>458</v>
       </c>
-      <c r="D30" t="s">
-        <v>426</v>
-      </c>
-      <c r="E30" t="s">
-        <v>150</v>
-      </c>
-      <c r="F30" t="s">
-        <v>150</v>
-      </c>
-      <c r="G30" t="s">
-        <v>197</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B39" t="s">
         <v>459</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D39" t="s">
+        <v>408</v>
+      </c>
+      <c r="E39" t="s">
+        <v>150</v>
+      </c>
+      <c r="F39" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" t="s">
+        <v>197</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
         <v>460</v>
       </c>
-      <c r="D31" t="s">
-        <v>426</v>
-      </c>
-      <c r="E31" t="s">
-        <v>150</v>
-      </c>
-      <c r="F31" t="s">
-        <v>150</v>
-      </c>
-      <c r="G31" t="s">
-        <v>197</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B40" t="s">
         <v>461</v>
       </c>
-      <c r="B32" t="s">
+      <c r="D40" t="s">
+        <v>423</v>
+      </c>
+      <c r="E40" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40" t="s">
+        <v>197</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
         <v>462</v>
       </c>
-      <c r="D32" t="s">
-        <v>426</v>
-      </c>
-      <c r="E32" t="s">
-        <v>150</v>
-      </c>
-      <c r="F32" t="s">
-        <v>150</v>
-      </c>
-      <c r="G32" t="s">
-        <v>197</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B41" t="s">
         <v>463</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D41" t="s">
+        <v>408</v>
+      </c>
+      <c r="E41" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" t="s">
+        <v>150</v>
+      </c>
+      <c r="G41" t="s">
+        <v>197</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
         <v>464</v>
       </c>
-      <c r="D33" t="s">
-        <v>426</v>
-      </c>
-      <c r="E33" t="s">
-        <v>150</v>
-      </c>
-      <c r="F33" t="s">
-        <v>150</v>
-      </c>
-      <c r="G33" t="s">
-        <v>197</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B42" t="s">
         <v>465</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D42" t="s">
+        <v>423</v>
+      </c>
+      <c r="E42" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" t="s">
+        <v>150</v>
+      </c>
+      <c r="G42" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
         <v>466</v>
       </c>
-      <c r="D34" t="s">
-        <v>426</v>
-      </c>
-      <c r="E34" t="s">
-        <v>150</v>
-      </c>
-      <c r="F34" t="s">
-        <v>150</v>
-      </c>
-      <c r="G34" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B43" t="s">
         <v>467</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D43" t="s">
+        <v>423</v>
+      </c>
+      <c r="E43" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" t="s">
+        <v>150</v>
+      </c>
+      <c r="G43" t="s">
+        <v>197</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
         <v>468</v>
       </c>
-      <c r="D35" t="s">
-        <v>426</v>
-      </c>
-      <c r="E35" t="s">
-        <v>150</v>
-      </c>
-      <c r="F35" t="s">
-        <v>150</v>
-      </c>
-      <c r="G35" t="s">
-        <v>197</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B44" t="s">
         <v>469</v>
       </c>
-      <c r="B36" t="s">
+      <c r="D44" t="s">
+        <v>408</v>
+      </c>
+      <c r="E44" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" t="s">
+        <v>150</v>
+      </c>
+      <c r="G44" t="s">
+        <v>197</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
         <v>470</v>
       </c>
-      <c r="D36" t="s">
-        <v>410</v>
-      </c>
-      <c r="E36" t="s">
-        <v>150</v>
-      </c>
-      <c r="F36" t="s">
-        <v>150</v>
-      </c>
-      <c r="G36" t="s">
-        <v>197</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B45" t="s">
         <v>471</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D45" t="s">
+        <v>408</v>
+      </c>
+      <c r="E45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" t="s">
+        <v>150</v>
+      </c>
+      <c r="G45" t="s">
+        <v>197</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
         <v>472</v>
       </c>
-      <c r="D37" t="s">
-        <v>410</v>
-      </c>
-      <c r="E37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F37" t="s">
-        <v>150</v>
-      </c>
-      <c r="G37" t="s">
-        <v>197</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B46" t="s">
+        <v>540</v>
+      </c>
+      <c r="C46" t="s">
+        <v>518</v>
+      </c>
+      <c r="D46" t="s">
+        <v>423</v>
+      </c>
+      <c r="E46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" t="s">
+        <v>150</v>
+      </c>
+      <c r="G46" t="s">
+        <v>197</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
         <v>473</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B47" t="s">
+        <v>541</v>
+      </c>
+      <c r="C47" t="s">
+        <v>518</v>
+      </c>
+      <c r="D47" t="s">
+        <v>423</v>
+      </c>
+      <c r="E47" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" t="s">
+        <v>197</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
         <v>474</v>
       </c>
-      <c r="D38" t="s">
-        <v>426</v>
-      </c>
-      <c r="E38" t="s">
-        <v>150</v>
-      </c>
-      <c r="F38" t="s">
-        <v>150</v>
-      </c>
-      <c r="G38" t="s">
-        <v>197</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B48" t="s">
+        <v>542</v>
+      </c>
+      <c r="C48" t="s">
+        <v>518</v>
+      </c>
+      <c r="D48" t="s">
+        <v>423</v>
+      </c>
+      <c r="E48" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" t="s">
+        <v>150</v>
+      </c>
+      <c r="G48" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
         <v>475</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B49" t="s">
         <v>476</v>
       </c>
-      <c r="D39" t="s">
-        <v>426</v>
-      </c>
-      <c r="E39" t="s">
-        <v>150</v>
-      </c>
-      <c r="F39" t="s">
-        <v>150</v>
-      </c>
-      <c r="G39" t="s">
-        <v>197</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="D49" t="s">
+        <v>423</v>
+      </c>
+      <c r="E49" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" t="s">
+        <v>150</v>
+      </c>
+      <c r="G49" t="s">
+        <v>197</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
         <v>477</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B50" t="s">
+        <v>543</v>
+      </c>
+      <c r="C50" t="s">
+        <v>518</v>
+      </c>
+      <c r="D50" t="s">
+        <v>423</v>
+      </c>
+      <c r="E50" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" t="s">
+        <v>197</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
         <v>478</v>
       </c>
-      <c r="D40" t="s">
-        <v>410</v>
-      </c>
-      <c r="E40" t="s">
-        <v>150</v>
-      </c>
-      <c r="F40" t="s">
-        <v>150</v>
-      </c>
-      <c r="G40" t="s">
-        <v>197</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B51" t="s">
+        <v>544</v>
+      </c>
+      <c r="C51" t="s">
+        <v>518</v>
+      </c>
+      <c r="D51" t="s">
+        <v>423</v>
+      </c>
+      <c r="E51" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" t="s">
+        <v>197</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
         <v>479</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B52" t="s">
+        <v>507</v>
+      </c>
+      <c r="C52" t="s">
+        <v>517</v>
+      </c>
+      <c r="E52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F52" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" t="s">
+        <v>197</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
         <v>480</v>
       </c>
-      <c r="D41" t="s">
-        <v>426</v>
-      </c>
-      <c r="E41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F41" t="s">
-        <v>150</v>
-      </c>
-      <c r="G41" t="s">
-        <v>197</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B53" t="s">
+        <v>511</v>
+      </c>
+      <c r="C53" t="s">
+        <v>517</v>
+      </c>
+      <c r="D53" t="s">
+        <v>408</v>
+      </c>
+      <c r="E53" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" t="s">
+        <v>197</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
         <v>481</v>
-      </c>
-      <c r="B42" t="s">
-        <v>482</v>
-      </c>
-      <c r="D42" t="s">
-        <v>410</v>
-      </c>
-      <c r="E42" t="s">
-        <v>150</v>
-      </c>
-      <c r="F42" t="s">
-        <v>150</v>
-      </c>
-      <c r="G42" t="s">
-        <v>197</v>
-      </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
-      <c r="I42" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>483</v>
-      </c>
-      <c r="B43" t="s">
-        <v>484</v>
-      </c>
-      <c r="D43" t="s">
-        <v>426</v>
-      </c>
-      <c r="E43" t="s">
-        <v>150</v>
-      </c>
-      <c r="F43" t="s">
-        <v>150</v>
-      </c>
-      <c r="G43" t="s">
-        <v>197</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>485</v>
-      </c>
-      <c r="B44" t="s">
-        <v>486</v>
-      </c>
-      <c r="D44" t="s">
-        <v>410</v>
-      </c>
-      <c r="E44" t="s">
-        <v>150</v>
-      </c>
-      <c r="F44" t="s">
-        <v>150</v>
-      </c>
-      <c r="G44" t="s">
-        <v>197</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>487</v>
-      </c>
-      <c r="B45" t="s">
-        <v>488</v>
-      </c>
-      <c r="D45" t="s">
-        <v>426</v>
-      </c>
-      <c r="E45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F45" t="s">
-        <v>150</v>
-      </c>
-      <c r="G45" t="s">
-        <v>197</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>489</v>
-      </c>
-      <c r="B46" t="s">
-        <v>490</v>
-      </c>
-      <c r="D46" t="s">
-        <v>426</v>
-      </c>
-      <c r="E46" t="s">
-        <v>150</v>
-      </c>
-      <c r="F46" t="s">
-        <v>150</v>
-      </c>
-      <c r="G46" t="s">
-        <v>197</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>491</v>
-      </c>
-      <c r="B47" t="s">
-        <v>492</v>
-      </c>
-      <c r="D47" t="s">
-        <v>410</v>
-      </c>
-      <c r="E47" t="s">
-        <v>150</v>
-      </c>
-      <c r="F47" t="s">
-        <v>150</v>
-      </c>
-      <c r="G47" t="s">
-        <v>197</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>493</v>
-      </c>
-      <c r="B48" t="s">
-        <v>494</v>
-      </c>
-      <c r="D48" t="s">
-        <v>410</v>
-      </c>
-      <c r="E48" t="s">
-        <v>150</v>
-      </c>
-      <c r="F48" t="s">
-        <v>150</v>
-      </c>
-      <c r="G48" t="s">
-        <v>197</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>495</v>
-      </c>
-      <c r="B49" t="s">
-        <v>496</v>
-      </c>
-      <c r="D49" t="s">
-        <v>426</v>
-      </c>
-      <c r="E49" t="s">
-        <v>150</v>
-      </c>
-      <c r="F49" t="s">
-        <v>150</v>
-      </c>
-      <c r="G49" t="s">
-        <v>197</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>497</v>
-      </c>
-      <c r="B50" t="s">
-        <v>498</v>
-      </c>
-      <c r="D50" t="s">
-        <v>426</v>
-      </c>
-      <c r="E50" t="s">
-        <v>150</v>
-      </c>
-      <c r="F50" t="s">
-        <v>150</v>
-      </c>
-      <c r="G50" t="s">
-        <v>197</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>499</v>
-      </c>
-      <c r="B51" t="s">
-        <v>500</v>
-      </c>
-      <c r="D51" t="s">
-        <v>426</v>
-      </c>
-      <c r="E51" t="s">
-        <v>150</v>
-      </c>
-      <c r="F51" t="s">
-        <v>150</v>
-      </c>
-      <c r="G51" t="s">
-        <v>197</v>
-      </c>
-      <c r="H51">
-        <v>1</v>
-      </c>
-      <c r="I51" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>501</v>
-      </c>
-      <c r="B52" t="s">
-        <v>502</v>
-      </c>
-      <c r="D52" t="s">
-        <v>426</v>
-      </c>
-      <c r="E52" t="s">
-        <v>150</v>
-      </c>
-      <c r="F52" t="s">
-        <v>150</v>
-      </c>
-      <c r="G52" t="s">
-        <v>197</v>
-      </c>
-      <c r="H52">
-        <v>1</v>
-      </c>
-      <c r="I52" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>503</v>
-      </c>
-      <c r="B53" t="s">
-        <v>504</v>
-      </c>
-      <c r="D53" t="s">
-        <v>426</v>
-      </c>
-      <c r="E53" t="s">
-        <v>150</v>
-      </c>
-      <c r="F53" t="s">
-        <v>150</v>
-      </c>
-      <c r="G53" t="s">
-        <v>197</v>
-      </c>
-      <c r="H53">
-        <v>1</v>
-      </c>
-      <c r="I53" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>505</v>
       </c>
       <c r="B54" t="s">
         <v>506</v>
       </c>
+      <c r="C54" t="s">
+        <v>517</v>
+      </c>
       <c r="D54" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="E54" t="s">
         <v>150</v>
@@ -8872,18 +11141,24 @@
         <v>197</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s">
-        <v>535</v>
+        <v>483</v>
+      </c>
+      <c r="C55" t="s">
+        <v>517</v>
+      </c>
+      <c r="D55" t="s">
+        <v>419</v>
       </c>
       <c r="E55" t="s">
         <v>150</v>
@@ -8901,324 +11176,348 @@
         <v>400</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
+        <v>484</v>
+      </c>
+      <c r="B56" t="s">
+        <v>485</v>
+      </c>
+      <c r="C56" t="s">
+        <v>517</v>
+      </c>
+      <c r="D56" t="s">
+        <v>408</v>
+      </c>
+      <c r="E56" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" t="s">
+        <v>150</v>
+      </c>
+      <c r="G56" t="s">
+        <v>197</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>486</v>
+      </c>
+      <c r="B57" t="s">
+        <v>487</v>
+      </c>
+      <c r="C57" t="s">
+        <v>517</v>
+      </c>
+      <c r="D57" t="s">
+        <v>408</v>
+      </c>
+      <c r="E57" t="s">
+        <v>150</v>
+      </c>
+      <c r="F57" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" t="s">
+        <v>197</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>488</v>
+      </c>
+      <c r="B58" t="s">
+        <v>513</v>
+      </c>
+      <c r="C58" t="s">
+        <v>517</v>
+      </c>
+      <c r="D58" t="s">
+        <v>408</v>
+      </c>
+      <c r="E58" t="s">
+        <v>150</v>
+      </c>
+      <c r="F58" t="s">
+        <v>150</v>
+      </c>
+      <c r="G58" t="s">
+        <v>197</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>489</v>
+      </c>
+      <c r="B59" t="s">
+        <v>512</v>
+      </c>
+      <c r="C59" t="s">
+        <v>517</v>
+      </c>
+      <c r="D59" t="s">
+        <v>490</v>
+      </c>
+      <c r="E59" t="s">
+        <v>150</v>
+      </c>
+      <c r="F59" t="s">
+        <v>150</v>
+      </c>
+      <c r="G59" t="s">
+        <v>197</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>491</v>
+      </c>
+      <c r="B60" t="s">
         <v>508</v>
       </c>
-      <c r="B56" t="s">
-        <v>539</v>
-      </c>
-      <c r="D56" t="s">
-        <v>410</v>
-      </c>
-      <c r="E56" t="s">
-        <v>150</v>
-      </c>
-      <c r="F56" t="s">
-        <v>150</v>
-      </c>
-      <c r="G56" t="s">
-        <v>197</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="C60" t="s">
+        <v>517</v>
+      </c>
+      <c r="D60" t="s">
+        <v>492</v>
+      </c>
+      <c r="E60" t="s">
+        <v>150</v>
+      </c>
+      <c r="F60" t="s">
+        <v>150</v>
+      </c>
+      <c r="G60" t="s">
+        <v>197</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>493</v>
+      </c>
+      <c r="B61" t="s">
         <v>509</v>
       </c>
-      <c r="B57" t="s">
-        <v>534</v>
-      </c>
-      <c r="D57" t="s">
-        <v>410</v>
-      </c>
-      <c r="E57" t="s">
-        <v>150</v>
-      </c>
-      <c r="F57" t="s">
-        <v>150</v>
-      </c>
-      <c r="G57" t="s">
-        <v>197</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="C61" t="s">
+        <v>517</v>
+      </c>
+      <c r="D61" t="s">
+        <v>492</v>
+      </c>
+      <c r="E61" t="s">
+        <v>150</v>
+      </c>
+      <c r="F61" t="s">
+        <v>150</v>
+      </c>
+      <c r="G61" t="s">
+        <v>197</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>494</v>
+      </c>
+      <c r="B62" t="s">
         <v>510</v>
       </c>
-      <c r="B58" t="s">
-        <v>511</v>
-      </c>
-      <c r="D58" t="s">
-        <v>421</v>
-      </c>
-      <c r="E58" t="s">
-        <v>150</v>
-      </c>
-      <c r="F58" t="s">
-        <v>150</v>
-      </c>
-      <c r="G58" t="s">
-        <v>197</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>512</v>
-      </c>
-      <c r="B59" t="s">
-        <v>513</v>
-      </c>
-      <c r="D59" t="s">
-        <v>410</v>
-      </c>
-      <c r="E59" t="s">
-        <v>150</v>
-      </c>
-      <c r="F59" t="s">
-        <v>150</v>
-      </c>
-      <c r="G59" t="s">
-        <v>197</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
+      <c r="C62" t="s">
+        <v>517</v>
+      </c>
+      <c r="D62" t="s">
+        <v>492</v>
+      </c>
+      <c r="E62" t="s">
+        <v>150</v>
+      </c>
+      <c r="F62" t="s">
+        <v>150</v>
+      </c>
+      <c r="G62" t="s">
+        <v>197</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>495</v>
+      </c>
+      <c r="B63" t="s">
+        <v>496</v>
+      </c>
+      <c r="C63" t="s">
+        <v>517</v>
+      </c>
+      <c r="D63" t="s">
+        <v>497</v>
+      </c>
+      <c r="E63" t="s">
+        <v>150</v>
+      </c>
+      <c r="F63" t="s">
+        <v>150</v>
+      </c>
+      <c r="G63" t="s">
+        <v>197</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>498</v>
+      </c>
+      <c r="B64" t="s">
+        <v>499</v>
+      </c>
+      <c r="C64" t="s">
+        <v>517</v>
+      </c>
+      <c r="D64" t="s">
+        <v>497</v>
+      </c>
+      <c r="E64" t="s">
+        <v>150</v>
+      </c>
+      <c r="F64" t="s">
+        <v>150</v>
+      </c>
+      <c r="G64" t="s">
+        <v>197</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>500</v>
+      </c>
+      <c r="B65" t="s">
+        <v>515</v>
+      </c>
+      <c r="E65" t="s">
+        <v>150</v>
+      </c>
+      <c r="F65" t="s">
+        <v>150</v>
+      </c>
+      <c r="G65" t="s">
+        <v>197</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>501</v>
+      </c>
+      <c r="B66" t="s">
         <v>514</v>
       </c>
-      <c r="B60" t="s">
-        <v>515</v>
-      </c>
-      <c r="D60" t="s">
-        <v>410</v>
-      </c>
-      <c r="E60" t="s">
-        <v>150</v>
-      </c>
-      <c r="F60" t="s">
-        <v>150</v>
-      </c>
-      <c r="G60" t="s">
-        <v>197</v>
-      </c>
-      <c r="H60">
-        <v>1</v>
-      </c>
-      <c r="I60" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
+      <c r="E66" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" t="s">
+        <v>150</v>
+      </c>
+      <c r="G66" t="s">
+        <v>197</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>502</v>
+      </c>
+      <c r="B67" t="s">
         <v>516</v>
       </c>
-      <c r="B61" t="s">
-        <v>541</v>
-      </c>
-      <c r="D61" t="s">
-        <v>410</v>
-      </c>
-      <c r="E61" t="s">
-        <v>150</v>
-      </c>
-      <c r="F61" t="s">
-        <v>150</v>
-      </c>
-      <c r="G61" t="s">
-        <v>197</v>
-      </c>
-      <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="E67" t="s">
+        <v>150</v>
+      </c>
+      <c r="F67" t="s">
+        <v>150</v>
+      </c>
+      <c r="G67" t="s">
+        <v>197</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>503</v>
+      </c>
+      <c r="B68" t="s">
+        <v>504</v>
+      </c>
+      <c r="C68" t="s">
         <v>517</v>
       </c>
-      <c r="B62" t="s">
-        <v>540</v>
-      </c>
-      <c r="D62" t="s">
-        <v>518</v>
-      </c>
-      <c r="E62" t="s">
-        <v>150</v>
-      </c>
-      <c r="F62" t="s">
-        <v>150</v>
-      </c>
-      <c r="G62" t="s">
-        <v>197</v>
-      </c>
-      <c r="H62">
-        <v>1</v>
-      </c>
-      <c r="I62" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>519</v>
-      </c>
-      <c r="B63" t="s">
-        <v>536</v>
-      </c>
-      <c r="D63" t="s">
-        <v>520</v>
-      </c>
-      <c r="E63" t="s">
-        <v>150</v>
-      </c>
-      <c r="F63" t="s">
-        <v>150</v>
-      </c>
-      <c r="G63" t="s">
-        <v>197</v>
-      </c>
-      <c r="H63">
-        <v>1</v>
-      </c>
-      <c r="I63" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>521</v>
-      </c>
-      <c r="B64" t="s">
-        <v>537</v>
-      </c>
-      <c r="D64" t="s">
-        <v>520</v>
-      </c>
-      <c r="E64" t="s">
-        <v>150</v>
-      </c>
-      <c r="F64" t="s">
-        <v>150</v>
-      </c>
-      <c r="G64" t="s">
-        <v>197</v>
-      </c>
-      <c r="H64">
-        <v>1</v>
-      </c>
-      <c r="I64" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>522</v>
-      </c>
-      <c r="B65" t="s">
-        <v>538</v>
-      </c>
-      <c r="D65" t="s">
-        <v>520</v>
-      </c>
-      <c r="E65" t="s">
-        <v>150</v>
-      </c>
-      <c r="F65" t="s">
-        <v>150</v>
-      </c>
-      <c r="G65" t="s">
-        <v>197</v>
-      </c>
-      <c r="H65">
-        <v>1</v>
-      </c>
-      <c r="I65" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>523</v>
-      </c>
-      <c r="B66" t="s">
-        <v>524</v>
-      </c>
-      <c r="D66" t="s">
-        <v>525</v>
-      </c>
-      <c r="E66" t="s">
-        <v>150</v>
-      </c>
-      <c r="F66" t="s">
-        <v>150</v>
-      </c>
-      <c r="G66" t="s">
-        <v>197</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>526</v>
-      </c>
-      <c r="B67" t="s">
-        <v>527</v>
-      </c>
-      <c r="D67" t="s">
-        <v>525</v>
-      </c>
-      <c r="E67" t="s">
-        <v>150</v>
-      </c>
-      <c r="F67" t="s">
-        <v>150</v>
-      </c>
-      <c r="G67" t="s">
-        <v>197</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>543</v>
+      <c r="D68" t="s">
+        <v>505</v>
       </c>
       <c r="E68" t="s">
         <v>150</v>
@@ -9230,81 +11529,9 @@
         <v>197</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E69" t="s">
-        <v>150</v>
-      </c>
-      <c r="F69" t="s">
-        <v>150</v>
-      </c>
-      <c r="G69" t="s">
-        <v>197</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="E70" t="s">
-        <v>150</v>
-      </c>
-      <c r="F70" t="s">
-        <v>150</v>
-      </c>
-      <c r="G70" t="s">
-        <v>197</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>531</v>
-      </c>
-      <c r="B71" t="s">
-        <v>532</v>
-      </c>
-      <c r="D71" t="s">
-        <v>533</v>
-      </c>
-      <c r="E71" t="s">
-        <v>150</v>
-      </c>
-      <c r="F71" t="s">
-        <v>150</v>
-      </c>
-      <c r="G71" t="s">
-        <v>197</v>
-      </c>
-      <c r="H71">
-        <v>1</v>
-      </c>
-      <c r="I71" t="s">
         <v>400</v>
       </c>
     </row>

--- a/CMAP_variableMetadata_additions.xlsx
+++ b/CMAP_variableMetadata_additions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\GitHub_niskin\BWrepos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE99FE7-0508-4142-ABBA-857D7F693042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805B7EAA-4290-48EE-8F3D-2E104C968E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="1620" windowWidth="31080" windowHeight="17355" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="930" windowWidth="37740" windowHeight="19485" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="557">
   <si>
     <t>Program</t>
   </si>
@@ -1690,9 +1690,6 @@
     <t>Sample latitude (decimal fractions; -90 to 90)</t>
   </si>
   <si>
-    <t>particles_perL</t>
-  </si>
-  <si>
     <t>number of organisms per liter in the group where group is from data_provider_category_manual</t>
   </si>
   <si>
@@ -1702,7 +1699,22 @@
     <t>cruise identifier</t>
   </si>
   <si>
-    <t>cells per Liter</t>
+    <t>abundance_perL</t>
+  </si>
+  <si>
+    <t>Biovolume per L for the group where group is from data_provider_category_manual</t>
+  </si>
+  <si>
+    <t>um^3 / L</t>
+  </si>
+  <si>
+    <t>cells / Liter</t>
+  </si>
+  <si>
+    <t>biovolume_perL</t>
+  </si>
+  <si>
+    <t>BIOS-SCOPE, BIOS, Simons Foundation International, bio, biogeo, biogeochemistry, biology, flowCAM,Discrete, Bottle, cruise, Discrete, in situ, insitu, in-situ, North Atlantic Ocean, observation</t>
   </si>
 </sst>
 </file>
@@ -7501,7 +7513,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F9E499-8F3B-4962-B041-C7E33D10A5CD}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -7574,7 +7586,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7603,7 +7615,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7632,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7661,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7690,7 +7702,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -7719,15 +7731,15 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
+        <v>549</v>
+      </c>
+      <c r="B8" t="s">
         <v>550</v>
-      </c>
-      <c r="B8" t="s">
-        <v>551</v>
       </c>
       <c r="C8" t="s">
         <v>387</v>
@@ -7748,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -7777,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -7806,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -7835,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -7864,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7893,7 +7905,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7922,7 +7934,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -7951,7 +7963,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7980,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -8009,7 +8021,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -8038,7 +8050,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -8067,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -8096,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -8125,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -8154,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -8183,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -8212,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -8241,7 +8253,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -8270,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -8299,7 +8311,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -8328,7 +8340,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -8357,7 +8369,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -8386,7 +8398,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -8415,7 +8427,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -8444,7 +8456,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -8473,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -8502,7 +8514,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -8531,7 +8543,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -8560,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -8589,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -8618,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -8647,7 +8659,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -8676,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -8705,7 +8717,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -8734,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -8763,7 +8775,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -8792,7 +8804,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -8821,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -8850,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -8879,7 +8891,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -8908,7 +8920,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -8937,7 +8949,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -8966,7 +8978,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -8995,7 +9007,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -9024,7 +9036,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -9053,7 +9065,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -9082,7 +9094,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -9111,7 +9123,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -9140,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -9169,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -9198,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -9227,7 +9239,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -9256,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -9285,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -9314,7 +9326,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -9343,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -9372,7 +9384,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -9401,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -9430,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -9459,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -9488,7 +9500,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -9517,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -9546,7 +9558,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -9575,7 +9587,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -9604,21 +9616,21 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="4" t="s">
-        <v>548</v>
+      <c r="A73" t="s">
+        <v>555</v>
       </c>
       <c r="B73" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C73" t="s">
         <v>517</v>
       </c>
       <c r="D73" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E73" t="s">
         <v>150</v>
@@ -9633,7 +9645,36 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>400</v>
+        <v>556</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B74" t="s">
+        <v>548</v>
+      </c>
+      <c r="C74" t="s">
+        <v>517</v>
+      </c>
+      <c r="D74" t="s">
+        <v>554</v>
+      </c>
+      <c r="E74" t="s">
+        <v>150</v>
+      </c>
+      <c r="F74" t="s">
+        <v>150</v>
+      </c>
+      <c r="G74" t="s">
+        <v>197</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>556</v>
       </c>
     </row>
   </sheetData>

--- a/CMAP_variableMetadata_additions.xlsx
+++ b/CMAP_variableMetadata_additions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\GitHub_niskin\BWrepos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805B7EAA-4290-48EE-8F3D-2E104C968E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A936B9-851A-40C3-83FF-42F3B81EFDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="930" windowWidth="37740" windowHeight="19485" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27255" yWindow="4380" windowWidth="23100" windowHeight="16170" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="4" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="all_temp" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">PVST_BATS_PLANKTON!$A$5:$I$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">PVST_BATS_PLANKTON!$A$5:$I$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="559">
   <si>
     <t>Program</t>
   </si>
@@ -1715,6 +1715,12 @@
   </si>
   <si>
     <t>BIOS-SCOPE, BIOS, Simons Foundation International, bio, biogeo, biogeochemistry, biology, flowCAM,Discrete, Bottle, cruise, Discrete, in situ, insitu, in-situ, North Atlantic Ocean, observation</t>
+  </si>
+  <si>
+    <t>sampleType</t>
+  </si>
+  <si>
+    <t>use this to distinguish between different types of flowcam samples</t>
   </si>
 </sst>
 </file>
@@ -7513,7 +7519,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F9E499-8F3B-4962-B041-C7E33D10A5CD}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -7678,10 +7684,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>557</v>
       </c>
       <c r="B6" t="s">
-        <v>407</v>
+        <v>558</v>
       </c>
       <c r="C6" t="s">
         <v>387</v>
@@ -7707,10 +7713,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B7" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C7" t="s">
         <v>387</v>
@@ -7736,16 +7742,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>549</v>
+        <v>409</v>
       </c>
       <c r="B8" t="s">
-        <v>550</v>
+        <v>410</v>
       </c>
       <c r="C8" t="s">
         <v>387</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
         <v>150</v>
@@ -7754,7 +7760,7 @@
         <v>150</v>
       </c>
       <c r="G8" t="s">
-        <v>387</v>
+        <v>197</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -7765,16 +7771,16 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>411</v>
+        <v>549</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>550</v>
       </c>
       <c r="C9" t="s">
         <v>387</v>
       </c>
       <c r="D9" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
         <v>150</v>
@@ -7783,7 +7789,7 @@
         <v>150</v>
       </c>
       <c r="G9" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -7794,16 +7800,16 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B10" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C10" t="s">
         <v>387</v>
       </c>
       <c r="D10" t="s">
-        <v>408</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
         <v>150</v>
@@ -7823,16 +7829,16 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B11" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C11" t="s">
         <v>387</v>
       </c>
       <c r="D11" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E11" t="s">
         <v>150</v>
@@ -7852,16 +7858,16 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B12" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="C12" t="s">
         <v>387</v>
       </c>
       <c r="D12" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E12" t="s">
         <v>150</v>
@@ -7881,16 +7887,16 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>398</v>
       </c>
       <c r="C13" t="s">
         <v>387</v>
       </c>
       <c r="D13" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="E13" t="s">
         <v>150</v>
@@ -7910,16 +7916,16 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B14" t="s">
-        <v>421</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
         <v>387</v>
       </c>
       <c r="D14" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E14" t="s">
         <v>150</v>
@@ -7939,16 +7945,16 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B15" t="s">
-        <v>519</v>
+        <v>421</v>
       </c>
       <c r="C15" t="s">
-        <v>518</v>
+        <v>387</v>
       </c>
       <c r="D15" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E15" t="s">
         <v>150</v>
@@ -7960,7 +7966,7 @@
         <v>197</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="s">
         <v>556</v>
@@ -7968,10 +7974,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C16" t="s">
         <v>518</v>
@@ -7997,10 +8003,10 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B17" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C17" t="s">
         <v>518</v>
@@ -8026,10 +8032,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C18" t="s">
         <v>518</v>
@@ -8055,10 +8061,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B19" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C19" t="s">
         <v>518</v>
@@ -8084,10 +8090,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B20" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C20" t="s">
         <v>518</v>
@@ -8113,10 +8119,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B21" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C21" t="s">
         <v>518</v>
@@ -8142,10 +8148,10 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B22" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C22" t="s">
         <v>518</v>
@@ -8171,10 +8177,10 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B23" t="s">
-        <v>432</v>
+        <v>526</v>
       </c>
       <c r="C23" t="s">
         <v>518</v>
@@ -8200,10 +8206,10 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B24" t="s">
-        <v>527</v>
+        <v>432</v>
       </c>
       <c r="C24" t="s">
         <v>518</v>
@@ -8229,10 +8235,10 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B25" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C25" t="s">
         <v>518</v>
@@ -8258,10 +8264,10 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B26" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C26" t="s">
         <v>518</v>
@@ -8287,10 +8293,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B27" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C27" t="s">
         <v>518</v>
@@ -8316,10 +8322,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C28" t="s">
         <v>518</v>
@@ -8345,10 +8351,10 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B29" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C29" t="s">
         <v>518</v>
@@ -8374,10 +8380,10 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B30" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C30" t="s">
         <v>518</v>
@@ -8403,10 +8409,10 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B31" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C31" t="s">
         <v>518</v>
@@ -8432,10 +8438,10 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B32" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C32" t="s">
         <v>518</v>
@@ -8461,10 +8467,10 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B33" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C33" t="s">
         <v>518</v>
@@ -8490,10 +8496,10 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B34" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C34" t="s">
         <v>518</v>
@@ -8519,10 +8525,10 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B35" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C35" t="s">
         <v>518</v>
@@ -8548,10 +8554,10 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B36" t="s">
-        <v>446</v>
+        <v>538</v>
       </c>
       <c r="C36" t="s">
         <v>518</v>
@@ -8577,16 +8583,16 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B37" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C37" t="s">
         <v>518</v>
       </c>
       <c r="D37" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="E37" t="s">
         <v>150</v>
@@ -8606,10 +8612,10 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B38" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C38" t="s">
         <v>518</v>
@@ -8635,16 +8641,16 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B39" t="s">
-        <v>539</v>
+        <v>450</v>
       </c>
       <c r="C39" t="s">
         <v>518</v>
       </c>
       <c r="D39" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E39" t="s">
         <v>150</v>
@@ -8664,10 +8670,10 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B40" t="s">
-        <v>453</v>
+        <v>539</v>
       </c>
       <c r="C40" t="s">
         <v>518</v>
@@ -8693,16 +8699,16 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B41" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C41" t="s">
         <v>518</v>
       </c>
       <c r="D41" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="E41" t="s">
         <v>150</v>
@@ -8722,16 +8728,16 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B42" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C42" t="s">
         <v>518</v>
       </c>
       <c r="D42" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E42" t="s">
         <v>150</v>
@@ -8751,16 +8757,16 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B43" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C43" t="s">
         <v>518</v>
       </c>
       <c r="D43" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="E43" t="s">
         <v>150</v>
@@ -8780,16 +8786,16 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B44" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C44" t="s">
         <v>518</v>
       </c>
       <c r="D44" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E44" t="s">
         <v>150</v>
@@ -8809,16 +8815,16 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B45" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C45" t="s">
         <v>518</v>
       </c>
       <c r="D45" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="E45" t="s">
         <v>150</v>
@@ -8838,16 +8844,16 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B46" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C46" t="s">
         <v>518</v>
       </c>
       <c r="D46" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E46" t="s">
         <v>150</v>
@@ -8867,10 +8873,10 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B47" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C47" t="s">
         <v>518</v>
@@ -8896,16 +8902,16 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B48" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C48" t="s">
         <v>518</v>
       </c>
       <c r="D48" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="E48" t="s">
         <v>150</v>
@@ -8925,10 +8931,10 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B49" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C49" t="s">
         <v>518</v>
@@ -8954,16 +8960,16 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B50" t="s">
-        <v>540</v>
+        <v>471</v>
       </c>
       <c r="C50" t="s">
         <v>518</v>
       </c>
       <c r="D50" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E50" t="s">
         <v>150</v>
@@ -8983,10 +8989,10 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B51" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C51" t="s">
         <v>518</v>
@@ -9012,10 +9018,10 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B52" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C52" t="s">
         <v>518</v>
@@ -9041,10 +9047,10 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B53" t="s">
-        <v>476</v>
+        <v>542</v>
       </c>
       <c r="C53" t="s">
         <v>518</v>
@@ -9070,10 +9076,10 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s">
-        <v>543</v>
+        <v>476</v>
       </c>
       <c r="C54" t="s">
         <v>518</v>
@@ -9099,10 +9105,10 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C55" t="s">
         <v>518</v>
@@ -9128,16 +9134,16 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="C56" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D56" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="E56" t="s">
         <v>150</v>
@@ -9149,7 +9155,7 @@
         <v>197</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="s">
         <v>556</v>
@@ -9157,10 +9163,10 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B57" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C57" t="s">
         <v>517</v>
@@ -9186,10 +9192,10 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B58" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C58" t="s">
         <v>517</v>
@@ -9215,16 +9221,16 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="C59" t="s">
         <v>517</v>
       </c>
       <c r="D59" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="E59" t="s">
         <v>150</v>
@@ -9244,16 +9250,16 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C60" t="s">
         <v>517</v>
       </c>
       <c r="D60" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E60" t="s">
         <v>150</v>
@@ -9273,10 +9279,10 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B61" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C61" t="s">
         <v>517</v>
@@ -9294,7 +9300,7 @@
         <v>197</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="s">
         <v>556</v>
@@ -9302,10 +9308,10 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B62" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="C62" t="s">
         <v>517</v>
@@ -9331,16 +9337,16 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C63" t="s">
         <v>517</v>
       </c>
       <c r="D63" t="s">
-        <v>490</v>
+        <v>408</v>
       </c>
       <c r="E63" t="s">
         <v>150</v>
@@ -9360,16 +9366,16 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C64" t="s">
         <v>517</v>
       </c>
       <c r="D64" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E64" t="s">
         <v>150</v>
@@ -9389,10 +9395,10 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C65" t="s">
         <v>517</v>
@@ -9418,10 +9424,10 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C66" t="s">
         <v>517</v>
@@ -9447,16 +9453,16 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="C67" t="s">
         <v>517</v>
       </c>
       <c r="D67" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E67" t="s">
         <v>150</v>
@@ -9468,7 +9474,7 @@
         <v>197</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="s">
         <v>556</v>
@@ -9476,10 +9482,10 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B68" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C68" t="s">
         <v>517</v>
@@ -9505,16 +9511,16 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B69" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="C69" t="s">
         <v>517</v>
       </c>
       <c r="D69" t="s">
-        <v>419</v>
+        <v>497</v>
       </c>
       <c r="E69" t="s">
         <v>150</v>
@@ -9534,16 +9540,16 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B70" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C70" t="s">
         <v>517</v>
       </c>
       <c r="D70" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E70" t="s">
         <v>150</v>
@@ -9563,10 +9569,10 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C71" t="s">
         <v>517</v>
@@ -9592,16 +9598,16 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
       <c r="C72" t="s">
         <v>517</v>
       </c>
       <c r="D72" t="s">
-        <v>505</v>
+        <v>408</v>
       </c>
       <c r="E72" t="s">
         <v>150</v>
@@ -9613,7 +9619,7 @@
         <v>197</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="s">
         <v>556</v>
@@ -9621,16 +9627,16 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>555</v>
+        <v>503</v>
       </c>
       <c r="B73" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C73" t="s">
         <v>517</v>
       </c>
       <c r="D73" t="s">
-        <v>553</v>
+        <v>505</v>
       </c>
       <c r="E73" t="s">
         <v>150</v>
@@ -9649,31 +9655,60 @@
       </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="4" t="s">
-        <v>551</v>
+      <c r="A74" t="s">
+        <v>555</v>
       </c>
       <c r="B74" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C74" t="s">
         <v>517</v>
       </c>
       <c r="D74" t="s">
+        <v>553</v>
+      </c>
+      <c r="E74" t="s">
+        <v>150</v>
+      </c>
+      <c r="F74" t="s">
+        <v>150</v>
+      </c>
+      <c r="G74" t="s">
+        <v>197</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B75" t="s">
+        <v>548</v>
+      </c>
+      <c r="C75" t="s">
+        <v>517</v>
+      </c>
+      <c r="D75" t="s">
         <v>554</v>
       </c>
-      <c r="E74" t="s">
-        <v>150</v>
-      </c>
-      <c r="F74" t="s">
-        <v>150</v>
-      </c>
-      <c r="G74" t="s">
-        <v>197</v>
-      </c>
-      <c r="H74">
-        <v>1</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="E75" t="s">
+        <v>150</v>
+      </c>
+      <c r="F75" t="s">
+        <v>150</v>
+      </c>
+      <c r="G75" t="s">
+        <v>197</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
         <v>556</v>
       </c>
     </row>

--- a/CMAP_variableMetadata_additions.xlsx
+++ b/CMAP_variableMetadata_additions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\GitHub_niskin\BWrepos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A936B9-851A-40C3-83FF-42F3B81EFDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91F649E-C51D-4054-A48D-EA0DE5F0D34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27255" yWindow="4380" windowWidth="23100" windowHeight="16170" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27630" yWindow="3885" windowWidth="26595" windowHeight="16365" firstSheet="4" activeTab="8" xr2:uid="{838CA6DE-4AAC-45DB-B6F8-47923BA10D1F}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="4" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="964684_v1_amino_acids_biosscope" sheetId="9" r:id="rId6"/>
     <sheet name="920443_v1_biosscope_in_situ_pum" sheetId="10" r:id="rId7"/>
     <sheet name="PVST_BATS_PLANKTON" sheetId="11" r:id="rId8"/>
-    <sheet name="all_temp" sheetId="12" r:id="rId9"/>
+    <sheet name="1000939_v1_bios_scope_ctd" sheetId="13" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">PVST_BATS_PLANKTON!$A$5:$I$73</definedName>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2325" uniqueCount="615">
   <si>
     <t>Program</t>
   </si>
@@ -1246,9 +1246,6 @@
     <t>hh:mm:ss</t>
   </si>
   <si>
-    <t>BIOS-SCOPE, BIOS, Simons Foundation International, bio, biogeo, biogeochemistry, biology, flowCAM, Zooscan, net tows, Discrete, Bottle, cruise, Discrete, in situ, insitu, in-situ, North Atlantic Ocean, observation</t>
-  </si>
-  <si>
     <t>degrees</t>
   </si>
   <si>
@@ -1558,9 +1555,6 @@
     <t>biovolume</t>
   </si>
   <si>
-    <t>Biovolume for the target detected within the ROI determined by means specified in the biovolume calculation method or protocol document.</t>
-  </si>
-  <si>
     <t>um^3</t>
   </si>
   <si>
@@ -1721,6 +1715,180 @@
   </si>
   <si>
     <t>use this to distinguish between different types of flowcam samples</t>
+  </si>
+  <si>
+    <t>cast</t>
+  </si>
+  <si>
+    <t>dimensionless</t>
+  </si>
+  <si>
+    <t>HHMM</t>
+  </si>
+  <si>
+    <t>decibars (db)</t>
+  </si>
+  <si>
+    <t>fluor</t>
+  </si>
+  <si>
+    <t>par</t>
+  </si>
+  <si>
+    <t>BIOS-SCOPE, BIOS, Simons Foundation International,  cruise, in situ, insitu, in-situ, North Atlantic Ocean, observation</t>
+  </si>
+  <si>
+    <t>Consecutive cast number for the instrument</t>
+  </si>
+  <si>
+    <t>par0</t>
+  </si>
+  <si>
+    <t>z_par_1pcnt</t>
+  </si>
+  <si>
+    <t>z_par_halfpcnt</t>
+  </si>
+  <si>
+    <t>z_par_tenthpcnt</t>
+  </si>
+  <si>
+    <t>pr</t>
+  </si>
+  <si>
+    <t>te</t>
+  </si>
+  <si>
+    <t>co</t>
+  </si>
+  <si>
+    <t>sa</t>
+  </si>
+  <si>
+    <t>o2</t>
+  </si>
+  <si>
+    <t>bac</t>
+  </si>
+  <si>
+    <t>fluor_filt</t>
+  </si>
+  <si>
+    <t>par_est</t>
+  </si>
+  <si>
+    <t>th</t>
+  </si>
+  <si>
+    <t>sig0</t>
+  </si>
+  <si>
+    <t>rho</t>
+  </si>
+  <si>
+    <t>bvfrq</t>
+  </si>
+  <si>
+    <t>vertZone</t>
+  </si>
+  <si>
+    <t>Cruise number</t>
+  </si>
+  <si>
+    <t>Mixed layer depth defined by surface density + 0.125 kg/m^3 (Suga, T., K. Motoki, Y. Aoki, and A. M. Macdonald (2004), The North Pacific climatology of winter mixed layer and mode waters, J. Phys. Oceanogr., 34, 3 – 22,10.1175/1520-0485(2004)034&lt;0003:TNPCOW&gt;2.0.CO;2)</t>
+  </si>
+  <si>
+    <t>Depth of 'active mixing' defined by buoyancy frequency (Morison, F., E. Harvey, G. Franzè and S. Menden-Deuer (2019). Storm-Induced Predator-Prey Decoupling Promotes Springtime Accumulation of North Atlantic Phytoplankton. Frontiers in Marine Science Volume 6 - 2019. DOI: 10.3389/fmars.2019.00608) and (Graff, J. R. and M. J. Behrenfeld (2018). Photoacclimation Responses in Subarctic Atlantic Phytoplankton Following a Natural Mixing-Restratification Event. Frontiers in Marine Science Volume 5 - 2018. DOI: 10.3389/fmars.2018.00209)"</t>
+  </si>
+  <si>
+    <t>meters</t>
+  </si>
+  <si>
+    <t>MLD from Thermal Expansion Coeff, and dT=0.2 deg C (Sprintall, J., and M. Tomczak (1992), Evidence of the barrier layer in the surface layer of the tropics, J. Geophys. Res., 97, 7305– 7316,10.1029/92JC00407)</t>
+  </si>
+  <si>
+    <t>Season designation (1 = mixed, 2  = spring, 3 = stratified, 4 = fall)</t>
+  </si>
+  <si>
+    <t>Surface PAR value</t>
+  </si>
+  <si>
+    <t>microeinsteins per meter squared per second (uE/m2/s)</t>
+  </si>
+  <si>
+    <t>Depth of 1% light level</t>
+  </si>
+  <si>
+    <t>Depth of 0.5% light level</t>
+  </si>
+  <si>
+    <t>Depth of 0.1% light level</t>
+  </si>
+  <si>
+    <t>time of sunrise</t>
+  </si>
+  <si>
+    <t>time of sunset</t>
+  </si>
+  <si>
+    <t>Vertical Zone designation (see description in Curry et al. 2026)</t>
+  </si>
+  <si>
+    <t>Brunt-Vaisala Frequency squared (N^2)</t>
+  </si>
+  <si>
+    <t>Density of seawater</t>
+  </si>
+  <si>
+    <t>Potential temperature as per UNESCO 1983 report</t>
+  </si>
+  <si>
+    <t>Photosynthetically Active Radiation (PAR): fitted exponential profile</t>
+  </si>
+  <si>
+    <t>Photosynthetically Active Radiation (PAR)</t>
+  </si>
+  <si>
+    <t>Fluorescence filtered (applies a 3rd order butterworth filter to the fluorometer profile)</t>
+  </si>
+  <si>
+    <t>Fluorescence</t>
+  </si>
+  <si>
+    <t>Beam Attenuation Coefficient</t>
+  </si>
+  <si>
+    <t>Dissolved Oxygen</t>
+  </si>
+  <si>
+    <t>PSU</t>
+  </si>
+  <si>
+    <t>Salinity</t>
+  </si>
+  <si>
+    <t>Temperature (ITS-90)</t>
+  </si>
+  <si>
+    <t>S/m</t>
+  </si>
+  <si>
+    <t>reciprocal meters (1/m)</t>
+  </si>
+  <si>
+    <t>relative fluorescence units (RFU)</t>
+  </si>
+  <si>
+    <t>degree C (ITS-90)</t>
+  </si>
+  <si>
+    <t>Potential density relative to the reference pressure</t>
+  </si>
+  <si>
+    <t>kg/m^3</t>
+  </si>
+  <si>
+    <t>s^-2</t>
   </si>
 </sst>
 </file>
@@ -7586,27 +7754,27 @@
         <v>150</v>
       </c>
       <c r="G2" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C3" t="s">
         <v>387</v>
       </c>
       <c r="D3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E3" t="s">
         <v>150</v>
@@ -7615,27 +7783,27 @@
         <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B4" t="s">
         <v>402</v>
       </c>
-      <c r="B4" t="s">
-        <v>403</v>
-      </c>
       <c r="C4" t="s">
         <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E4" t="s">
         <v>150</v>
@@ -7644,21 +7812,21 @@
         <v>150</v>
       </c>
       <c r="G4" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B5" t="s">
         <v>404</v>
-      </c>
-      <c r="B5" t="s">
-        <v>405</v>
       </c>
       <c r="C5" t="s">
         <v>387</v>
@@ -7673,27 +7841,27 @@
         <v>150</v>
       </c>
       <c r="G5" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C6" t="s">
         <v>387</v>
       </c>
       <c r="D6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E6" t="s">
         <v>150</v>
@@ -7702,28 +7870,28 @@
         <v>150</v>
       </c>
       <c r="G6" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B7" t="s">
         <v>406</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D7" t="s">
         <v>407</v>
       </c>
-      <c r="C7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D7" t="s">
-        <v>408</v>
-      </c>
       <c r="E7" t="s">
         <v>150</v>
       </c>
@@ -7731,27 +7899,27 @@
         <v>150</v>
       </c>
       <c r="G7" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B8" t="s">
         <v>409</v>
       </c>
-      <c r="B8" t="s">
-        <v>410</v>
-      </c>
       <c r="C8" t="s">
         <v>387</v>
       </c>
       <c r="D8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E8" t="s">
         <v>150</v>
@@ -7760,21 +7928,21 @@
         <v>150</v>
       </c>
       <c r="G8" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B9" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C9" t="s">
         <v>387</v>
@@ -7795,15 +7963,15 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B10" t="s">
         <v>411</v>
-      </c>
-      <c r="B10" t="s">
-        <v>412</v>
       </c>
       <c r="C10" t="s">
         <v>387</v>
@@ -7818,27 +7986,27 @@
         <v>150</v>
       </c>
       <c r="G10" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B11" t="s">
         <v>413</v>
       </c>
-      <c r="B11" t="s">
-        <v>414</v>
-      </c>
       <c r="C11" t="s">
         <v>387</v>
       </c>
       <c r="D11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E11" t="s">
         <v>150</v>
@@ -7847,28 +8015,28 @@
         <v>150</v>
       </c>
       <c r="G11" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
+        <v>414</v>
+      </c>
+      <c r="B12" t="s">
         <v>415</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>387</v>
+      </c>
+      <c r="D12" t="s">
         <v>416</v>
       </c>
-      <c r="C12" t="s">
-        <v>387</v>
-      </c>
-      <c r="D12" t="s">
-        <v>417</v>
-      </c>
       <c r="E12" t="s">
         <v>150</v>
       </c>
@@ -7876,13 +8044,13 @@
         <v>150</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7905,18 +8073,18 @@
         <v>150</v>
       </c>
       <c r="G13" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B14" t="s">
         <v>211</v>
@@ -7925,7 +8093,7 @@
         <v>387</v>
       </c>
       <c r="D14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E14" t="s">
         <v>150</v>
@@ -7934,27 +8102,27 @@
         <v>150</v>
       </c>
       <c r="G14" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
+        <v>419</v>
+      </c>
+      <c r="B15" t="s">
         <v>420</v>
       </c>
-      <c r="B15" t="s">
-        <v>421</v>
-      </c>
       <c r="C15" t="s">
         <v>387</v>
       </c>
       <c r="D15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E15" t="s">
         <v>150</v>
@@ -7963,27 +8131,27 @@
         <v>150</v>
       </c>
       <c r="G15" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
+        <v>421</v>
+      </c>
+      <c r="B16" t="s">
+        <v>517</v>
+      </c>
+      <c r="C16" t="s">
+        <v>516</v>
+      </c>
+      <c r="D16" t="s">
         <v>422</v>
-      </c>
-      <c r="B16" t="s">
-        <v>519</v>
-      </c>
-      <c r="C16" t="s">
-        <v>518</v>
-      </c>
-      <c r="D16" t="s">
-        <v>423</v>
       </c>
       <c r="E16" t="s">
         <v>150</v>
@@ -7998,21 +8166,21 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C17" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D17" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E17" t="s">
         <v>150</v>
@@ -8027,21 +8195,21 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C18" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E18" t="s">
         <v>150</v>
@@ -8056,21 +8224,21 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B19" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C19" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D19" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E19" t="s">
         <v>150</v>
@@ -8085,21 +8253,21 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B20" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C20" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E20" t="s">
         <v>150</v>
@@ -8114,21 +8282,21 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B21" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C21" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D21" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E21" t="s">
         <v>150</v>
@@ -8143,21 +8311,21 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B22" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E22" t="s">
         <v>150</v>
@@ -8172,21 +8340,21 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B23" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C23" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D23" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E23" t="s">
         <v>150</v>
@@ -8201,21 +8369,21 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
+        <v>430</v>
+      </c>
+      <c r="B24" t="s">
         <v>431</v>
       </c>
-      <c r="B24" t="s">
-        <v>432</v>
-      </c>
       <c r="C24" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D24" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E24" t="s">
         <v>150</v>
@@ -8230,21 +8398,21 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B25" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C25" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D25" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E25" t="s">
         <v>150</v>
@@ -8259,21 +8427,21 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B26" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C26" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D26" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E26" t="s">
         <v>150</v>
@@ -8288,21 +8456,21 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B27" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C27" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D27" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E27" t="s">
         <v>150</v>
@@ -8317,21 +8485,21 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B28" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C28" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D28" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E28" t="s">
         <v>150</v>
@@ -8346,21 +8514,21 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B29" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C29" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D29" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E29" t="s">
         <v>150</v>
@@ -8375,21 +8543,21 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B30" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C30" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D30" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E30" t="s">
         <v>150</v>
@@ -8404,21 +8572,21 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B31" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C31" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E31" t="s">
         <v>150</v>
@@ -8433,21 +8601,21 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B32" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C32" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D32" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E32" t="s">
         <v>150</v>
@@ -8462,21 +8630,21 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B33" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C33" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D33" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E33" t="s">
         <v>150</v>
@@ -8491,21 +8659,21 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B34" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C34" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D34" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E34" t="s">
         <v>150</v>
@@ -8520,21 +8688,21 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B35" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C35" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D35" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E35" t="s">
         <v>150</v>
@@ -8549,21 +8717,21 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B36" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C36" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D36" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E36" t="s">
         <v>150</v>
@@ -8578,21 +8746,21 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
+        <v>444</v>
+      </c>
+      <c r="B37" t="s">
         <v>445</v>
       </c>
-      <c r="B37" t="s">
-        <v>446</v>
-      </c>
       <c r="C37" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D37" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E37" t="s">
         <v>150</v>
@@ -8607,21 +8775,21 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
+        <v>446</v>
+      </c>
+      <c r="B38" t="s">
         <v>447</v>
       </c>
-      <c r="B38" t="s">
-        <v>448</v>
-      </c>
       <c r="C38" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E38" t="s">
         <v>150</v>
@@ -8636,21 +8804,21 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
+        <v>448</v>
+      </c>
+      <c r="B39" t="s">
         <v>449</v>
       </c>
-      <c r="B39" t="s">
-        <v>450</v>
-      </c>
       <c r="C39" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D39" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E39" t="s">
         <v>150</v>
@@ -8665,21 +8833,21 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B40" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C40" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D40" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E40" t="s">
         <v>150</v>
@@ -8694,21 +8862,21 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
+        <v>451</v>
+      </c>
+      <c r="B41" t="s">
         <v>452</v>
       </c>
-      <c r="B41" t="s">
-        <v>453</v>
-      </c>
       <c r="C41" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D41" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E41" t="s">
         <v>150</v>
@@ -8723,21 +8891,21 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
+        <v>453</v>
+      </c>
+      <c r="B42" t="s">
         <v>454</v>
       </c>
-      <c r="B42" t="s">
-        <v>455</v>
-      </c>
       <c r="C42" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D42" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E42" t="s">
         <v>150</v>
@@ -8752,21 +8920,21 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
+        <v>455</v>
+      </c>
+      <c r="B43" t="s">
         <v>456</v>
       </c>
-      <c r="B43" t="s">
-        <v>457</v>
-      </c>
       <c r="C43" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D43" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E43" t="s">
         <v>150</v>
@@ -8781,21 +8949,21 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
+        <v>457</v>
+      </c>
+      <c r="B44" t="s">
         <v>458</v>
       </c>
-      <c r="B44" t="s">
-        <v>459</v>
-      </c>
       <c r="C44" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D44" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E44" t="s">
         <v>150</v>
@@ -8810,21 +8978,21 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
+        <v>459</v>
+      </c>
+      <c r="B45" t="s">
         <v>460</v>
       </c>
-      <c r="B45" t="s">
-        <v>461</v>
-      </c>
       <c r="C45" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D45" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E45" t="s">
         <v>150</v>
@@ -8839,21 +9007,21 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
+        <v>461</v>
+      </c>
+      <c r="B46" t="s">
         <v>462</v>
       </c>
-      <c r="B46" t="s">
-        <v>463</v>
-      </c>
       <c r="C46" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D46" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E46" t="s">
         <v>150</v>
@@ -8868,21 +9036,21 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
+        <v>463</v>
+      </c>
+      <c r="B47" t="s">
         <v>464</v>
       </c>
-      <c r="B47" t="s">
-        <v>465</v>
-      </c>
       <c r="C47" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D47" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E47" t="s">
         <v>150</v>
@@ -8897,21 +9065,21 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
+        <v>465</v>
+      </c>
+      <c r="B48" t="s">
         <v>466</v>
       </c>
-      <c r="B48" t="s">
-        <v>467</v>
-      </c>
       <c r="C48" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D48" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E48" t="s">
         <v>150</v>
@@ -8926,21 +9094,21 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
+        <v>467</v>
+      </c>
+      <c r="B49" t="s">
         <v>468</v>
       </c>
-      <c r="B49" t="s">
-        <v>469</v>
-      </c>
       <c r="C49" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D49" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E49" t="s">
         <v>150</v>
@@ -8955,21 +9123,21 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
+        <v>469</v>
+      </c>
+      <c r="B50" t="s">
         <v>470</v>
       </c>
-      <c r="B50" t="s">
-        <v>471</v>
-      </c>
       <c r="C50" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D50" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E50" t="s">
         <v>150</v>
@@ -8984,21 +9152,21 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B51" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C51" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D51" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E51" t="s">
         <v>150</v>
@@ -9013,21 +9181,21 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B52" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C52" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D52" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E52" t="s">
         <v>150</v>
@@ -9042,21 +9210,21 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C53" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D53" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E53" t="s">
         <v>150</v>
@@ -9071,21 +9239,21 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
+        <v>474</v>
+      </c>
+      <c r="B54" t="s">
         <v>475</v>
       </c>
-      <c r="B54" t="s">
-        <v>476</v>
-      </c>
       <c r="C54" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D54" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E54" t="s">
         <v>150</v>
@@ -9100,21 +9268,21 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C55" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E55" t="s">
         <v>150</v>
@@ -9129,21 +9297,21 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B56" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C56" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D56" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E56" t="s">
         <v>150</v>
@@ -9158,21 +9326,21 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B57" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C57" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D57" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E57" t="s">
         <v>150</v>
@@ -9187,21 +9355,21 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C58" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D58" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E58" t="s">
         <v>150</v>
@@ -9216,21 +9384,21 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C59" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D59" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E59" t="s">
         <v>150</v>
@@ -9245,21 +9413,21 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
+        <v>481</v>
+      </c>
+      <c r="B60" t="s">
         <v>482</v>
       </c>
-      <c r="B60" t="s">
-        <v>483</v>
-      </c>
       <c r="C60" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D60" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E60" t="s">
         <v>150</v>
@@ -9274,21 +9442,21 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
+        <v>483</v>
+      </c>
+      <c r="B61" t="s">
         <v>484</v>
       </c>
-      <c r="B61" t="s">
-        <v>485</v>
-      </c>
       <c r="C61" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D61" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E61" t="s">
         <v>150</v>
@@ -9303,21 +9471,21 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
+        <v>485</v>
+      </c>
+      <c r="B62" t="s">
         <v>486</v>
       </c>
-      <c r="B62" t="s">
-        <v>487</v>
-      </c>
       <c r="C62" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D62" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E62" t="s">
         <v>150</v>
@@ -9332,21 +9500,21 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B63" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C63" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D63" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E63" t="s">
         <v>150</v>
@@ -9361,21 +9529,21 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
+        <v>488</v>
+      </c>
+      <c r="B64" t="s">
+        <v>510</v>
+      </c>
+      <c r="C64" t="s">
+        <v>515</v>
+      </c>
+      <c r="D64" t="s">
         <v>489</v>
-      </c>
-      <c r="B64" t="s">
-        <v>512</v>
-      </c>
-      <c r="C64" t="s">
-        <v>517</v>
-      </c>
-      <c r="D64" t="s">
-        <v>490</v>
       </c>
       <c r="E64" t="s">
         <v>150</v>
@@ -9390,21 +9558,21 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
+        <v>490</v>
+      </c>
+      <c r="B65" t="s">
+        <v>506</v>
+      </c>
+      <c r="C65" t="s">
+        <v>515</v>
+      </c>
+      <c r="D65" t="s">
         <v>491</v>
-      </c>
-      <c r="B65" t="s">
-        <v>508</v>
-      </c>
-      <c r="C65" t="s">
-        <v>517</v>
-      </c>
-      <c r="D65" t="s">
-        <v>492</v>
       </c>
       <c r="E65" t="s">
         <v>150</v>
@@ -9419,21 +9587,21 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C66" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D66" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E66" t="s">
         <v>150</v>
@@ -9448,21 +9616,21 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C67" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D67" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E67" t="s">
         <v>150</v>
@@ -9477,21 +9645,21 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
+        <v>494</v>
+      </c>
+      <c r="B68" t="s">
         <v>495</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
+        <v>515</v>
+      </c>
+      <c r="D68" t="s">
         <v>496</v>
-      </c>
-      <c r="C68" t="s">
-        <v>517</v>
-      </c>
-      <c r="D68" t="s">
-        <v>497</v>
       </c>
       <c r="E68" t="s">
         <v>150</v>
@@ -9506,21 +9674,21 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
+        <v>497</v>
+      </c>
+      <c r="B69" t="s">
         <v>498</v>
       </c>
-      <c r="B69" t="s">
-        <v>499</v>
-      </c>
       <c r="C69" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D69" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E69" t="s">
         <v>150</v>
@@ -9535,21 +9703,21 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s">
+        <v>513</v>
+      </c>
+      <c r="C70" t="s">
         <v>515</v>
       </c>
-      <c r="C70" t="s">
-        <v>517</v>
-      </c>
       <c r="D70" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E70" t="s">
         <v>150</v>
@@ -9564,21 +9732,21 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C71" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D71" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E71" t="s">
         <v>150</v>
@@ -9593,21 +9761,21 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B72" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C72" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D72" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E72" t="s">
         <v>150</v>
@@ -9622,21 +9790,21 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
+        <v>502</v>
+      </c>
+      <c r="B73" t="s">
+        <v>543</v>
+      </c>
+      <c r="C73" t="s">
+        <v>515</v>
+      </c>
+      <c r="D73" t="s">
         <v>503</v>
-      </c>
-      <c r="B73" t="s">
-        <v>545</v>
-      </c>
-      <c r="C73" t="s">
-        <v>517</v>
-      </c>
-      <c r="D73" t="s">
-        <v>505</v>
       </c>
       <c r="E73" t="s">
         <v>150</v>
@@ -9651,21 +9819,21 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B74" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C74" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D74" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E74" t="s">
         <v>150</v>
@@ -9680,21 +9848,21 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B75" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C75" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D75" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E75" t="s">
         <v>150</v>
@@ -9709,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -9719,162 +9887,183 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41309215-EB4C-48B3-A3D7-89B6FA6A2DA4}">
-  <dimension ref="A1:I68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1936B2BD-9EC2-4ACF-BEDD-4E61EE334CEE}">
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="112.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="81.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" customWidth="1"/>
     <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B3" t="s">
         <v>402</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" t="s">
+        <v>387</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D4" t="s">
+        <v>558</v>
+      </c>
+      <c r="E4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>557</v>
+      </c>
+      <c r="B5" t="s">
+        <v>564</v>
+      </c>
+      <c r="C5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D5" t="s">
+        <v>558</v>
+      </c>
+      <c r="E5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5" t="s">
+        <v>387</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
         <v>403</v>
       </c>
-      <c r="D1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H1">
-        <v>0</v>
-      </c>
-      <c r="I1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="B6" t="s">
         <v>404</v>
       </c>
-      <c r="B2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D6" t="s">
         <v>192</v>
       </c>
-      <c r="E2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>406</v>
-      </c>
-      <c r="B3" t="s">
-        <v>407</v>
-      </c>
-      <c r="D3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>409</v>
-      </c>
-      <c r="B4" t="s">
-        <v>410</v>
-      </c>
-      <c r="D4" t="s">
-        <v>408</v>
-      </c>
-      <c r="E4" t="s">
-        <v>150</v>
-      </c>
-      <c r="F4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B5" t="s">
-        <v>412</v>
-      </c>
-      <c r="D5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" t="s">
-        <v>197</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>413</v>
-      </c>
-      <c r="B6" t="s">
-        <v>414</v>
-      </c>
-      <c r="D6" t="s">
-        <v>408</v>
-      </c>
       <c r="E6" t="s">
         <v>150</v>
       </c>
@@ -9882,24 +10071,27 @@
         <v>150</v>
       </c>
       <c r="G6" t="s">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75">
       <c r="A7" t="s">
-        <v>415</v>
-      </c>
-      <c r="B7" t="s">
-        <v>416</v>
+        <v>59</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="C7" t="s">
+        <v>392</v>
       </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>585</v>
       </c>
       <c r="E7" t="s">
         <v>150</v>
@@ -9907,25 +10099,28 @@
       <c r="F7" t="s">
         <v>150</v>
       </c>
-      <c r="G7" t="s">
-        <v>197</v>
+      <c r="G7" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75">
       <c r="A8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B8" t="s">
-        <v>398</v>
+        <v>60</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="C8" t="s">
+        <v>392</v>
       </c>
       <c r="D8" t="s">
-        <v>399</v>
+        <v>585</v>
       </c>
       <c r="E8" t="s">
         <v>150</v>
@@ -9933,25 +10128,28 @@
       <c r="F8" t="s">
         <v>150</v>
       </c>
-      <c r="G8" t="s">
-        <v>197</v>
+      <c r="G8" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75">
       <c r="A9" t="s">
-        <v>418</v>
-      </c>
-      <c r="B9" t="s">
-        <v>211</v>
+        <v>61</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="C9" t="s">
+        <v>392</v>
       </c>
       <c r="D9" t="s">
-        <v>419</v>
+        <v>585</v>
       </c>
       <c r="E9" t="s">
         <v>150</v>
@@ -9959,25 +10157,28 @@
       <c r="F9" t="s">
         <v>150</v>
       </c>
-      <c r="G9" t="s">
-        <v>197</v>
+      <c r="G9" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75">
       <c r="A10" t="s">
-        <v>420</v>
-      </c>
-      <c r="B10" t="s">
-        <v>421</v>
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" t="s">
+        <v>392</v>
       </c>
       <c r="D10" t="s">
-        <v>408</v>
+        <v>585</v>
       </c>
       <c r="E10" t="s">
         <v>150</v>
@@ -9985,28 +10186,28 @@
       <c r="F10" t="s">
         <v>150</v>
       </c>
-      <c r="G10" t="s">
-        <v>197</v>
+      <c r="G10" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75">
       <c r="A11" t="s">
-        <v>422</v>
-      </c>
-      <c r="B11" t="s">
-        <v>519</v>
+        <v>64</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>587</v>
       </c>
       <c r="C11" t="s">
-        <v>518</v>
+        <v>392</v>
       </c>
       <c r="D11" t="s">
-        <v>423</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>150</v>
@@ -10014,28 +10215,28 @@
       <c r="F11" t="s">
         <v>150</v>
       </c>
-      <c r="G11" t="s">
-        <v>197</v>
+      <c r="G11" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75">
       <c r="A12" t="s">
-        <v>424</v>
-      </c>
-      <c r="B12" t="s">
-        <v>520</v>
+        <v>57</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>593</v>
       </c>
       <c r="C12" t="s">
-        <v>518</v>
+        <v>392</v>
       </c>
       <c r="D12" t="s">
-        <v>423</v>
+        <v>559</v>
       </c>
       <c r="E12" t="s">
         <v>150</v>
@@ -10043,28 +10244,28 @@
       <c r="F12" t="s">
         <v>150</v>
       </c>
-      <c r="G12" t="s">
-        <v>197</v>
+      <c r="G12" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75">
       <c r="A13" t="s">
-        <v>425</v>
-      </c>
-      <c r="B13" t="s">
-        <v>521</v>
+        <v>58</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>594</v>
       </c>
       <c r="C13" t="s">
-        <v>518</v>
+        <v>392</v>
       </c>
       <c r="D13" t="s">
-        <v>423</v>
+        <v>559</v>
       </c>
       <c r="E13" t="s">
         <v>150</v>
@@ -10072,28 +10273,28 @@
       <c r="F13" t="s">
         <v>150</v>
       </c>
-      <c r="G13" t="s">
-        <v>197</v>
+      <c r="G13" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75">
       <c r="A14" t="s">
-        <v>426</v>
-      </c>
-      <c r="B14" t="s">
-        <v>522</v>
+        <v>565</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>588</v>
       </c>
       <c r="C14" t="s">
-        <v>518</v>
-      </c>
-      <c r="D14" t="s">
-        <v>423</v>
+        <v>383</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>589</v>
       </c>
       <c r="E14" t="s">
         <v>150</v>
@@ -10101,28 +10302,28 @@
       <c r="F14" t="s">
         <v>150</v>
       </c>
-      <c r="G14" t="s">
-        <v>197</v>
+      <c r="G14" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75">
       <c r="A15" t="s">
-        <v>427</v>
-      </c>
-      <c r="B15" t="s">
-        <v>523</v>
+        <v>566</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>590</v>
       </c>
       <c r="C15" t="s">
-        <v>518</v>
+        <v>392</v>
       </c>
       <c r="D15" t="s">
-        <v>423</v>
+        <v>585</v>
       </c>
       <c r="E15" t="s">
         <v>150</v>
@@ -10130,28 +10331,28 @@
       <c r="F15" t="s">
         <v>150</v>
       </c>
-      <c r="G15" t="s">
-        <v>197</v>
+      <c r="G15" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75">
       <c r="A16" t="s">
-        <v>428</v>
-      </c>
-      <c r="B16" t="s">
-        <v>524</v>
+        <v>567</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>591</v>
       </c>
       <c r="C16" t="s">
-        <v>518</v>
+        <v>392</v>
       </c>
       <c r="D16" t="s">
-        <v>423</v>
+        <v>585</v>
       </c>
       <c r="E16" t="s">
         <v>150</v>
@@ -10159,28 +10360,28 @@
       <c r="F16" t="s">
         <v>150</v>
       </c>
-      <c r="G16" t="s">
-        <v>197</v>
+      <c r="G16" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75">
       <c r="A17" t="s">
-        <v>429</v>
-      </c>
-      <c r="B17" t="s">
-        <v>525</v>
+        <v>568</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>592</v>
       </c>
       <c r="C17" t="s">
-        <v>518</v>
+        <v>392</v>
       </c>
       <c r="D17" t="s">
-        <v>423</v>
+        <v>585</v>
       </c>
       <c r="E17" t="s">
         <v>150</v>
@@ -10188,28 +10389,28 @@
       <c r="F17" t="s">
         <v>150</v>
       </c>
-      <c r="G17" t="s">
-        <v>197</v>
+      <c r="G17" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75">
       <c r="A18" t="s">
-        <v>430</v>
+        <v>569</v>
       </c>
       <c r="B18" t="s">
-        <v>526</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D18" t="s">
-        <v>423</v>
+        <v>560</v>
       </c>
       <c r="E18" t="s">
         <v>150</v>
@@ -10217,25 +10418,28 @@
       <c r="F18" t="s">
         <v>150</v>
       </c>
-      <c r="G18" t="s">
-        <v>197</v>
+      <c r="G18" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75">
       <c r="A19" t="s">
-        <v>431</v>
+        <v>570</v>
       </c>
       <c r="B19" t="s">
-        <v>432</v>
+        <v>607</v>
+      </c>
+      <c r="C19" t="s">
+        <v>383</v>
       </c>
       <c r="D19" t="s">
-        <v>423</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
         <v>150</v>
@@ -10243,28 +10447,28 @@
       <c r="F19" t="s">
         <v>150</v>
       </c>
-      <c r="G19" t="s">
-        <v>197</v>
+      <c r="G19" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75">
       <c r="A20" t="s">
-        <v>433</v>
+        <v>571</v>
       </c>
       <c r="B20" t="s">
-        <v>527</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D20" t="s">
-        <v>423</v>
+        <v>608</v>
       </c>
       <c r="E20" t="s">
         <v>150</v>
@@ -10272,28 +10476,28 @@
       <c r="F20" t="s">
         <v>150</v>
       </c>
-      <c r="G20" t="s">
-        <v>197</v>
+      <c r="G20" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75">
       <c r="A21" t="s">
-        <v>434</v>
+        <v>572</v>
       </c>
       <c r="B21" t="s">
-        <v>528</v>
+        <v>606</v>
       </c>
       <c r="C21" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D21" t="s">
-        <v>423</v>
+        <v>605</v>
       </c>
       <c r="E21" t="s">
         <v>150</v>
@@ -10301,28 +10505,28 @@
       <c r="F21" t="s">
         <v>150</v>
       </c>
-      <c r="G21" t="s">
-        <v>197</v>
+      <c r="G21" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75">
       <c r="A22" t="s">
-        <v>435</v>
+        <v>573</v>
       </c>
       <c r="B22" t="s">
-        <v>529</v>
+        <v>604</v>
       </c>
       <c r="C22" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D22" t="s">
-        <v>423</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
         <v>150</v>
@@ -10330,28 +10534,28 @@
       <c r="F22" t="s">
         <v>150</v>
       </c>
-      <c r="G22" t="s">
-        <v>197</v>
+      <c r="G22" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75">
       <c r="A23" t="s">
-        <v>436</v>
+        <v>574</v>
       </c>
       <c r="B23" t="s">
-        <v>530</v>
+        <v>603</v>
       </c>
       <c r="C23" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D23" t="s">
-        <v>423</v>
+        <v>609</v>
       </c>
       <c r="E23" t="s">
         <v>150</v>
@@ -10359,28 +10563,28 @@
       <c r="F23" t="s">
         <v>150</v>
       </c>
-      <c r="G23" t="s">
-        <v>197</v>
+      <c r="G23" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75">
       <c r="A24" t="s">
-        <v>437</v>
+        <v>561</v>
       </c>
       <c r="B24" t="s">
-        <v>531</v>
+        <v>602</v>
       </c>
       <c r="C24" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D24" t="s">
-        <v>423</v>
+        <v>610</v>
       </c>
       <c r="E24" t="s">
         <v>150</v>
@@ -10388,28 +10592,28 @@
       <c r="F24" t="s">
         <v>150</v>
       </c>
-      <c r="G24" t="s">
-        <v>197</v>
+      <c r="G24" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75">
       <c r="A25" t="s">
-        <v>438</v>
+        <v>575</v>
       </c>
       <c r="B25" t="s">
-        <v>532</v>
+        <v>601</v>
       </c>
       <c r="C25" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D25" t="s">
-        <v>423</v>
+        <v>610</v>
       </c>
       <c r="E25" t="s">
         <v>150</v>
@@ -10417,28 +10621,28 @@
       <c r="F25" t="s">
         <v>150</v>
       </c>
-      <c r="G25" t="s">
-        <v>197</v>
+      <c r="G25" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75">
       <c r="A26" t="s">
-        <v>439</v>
+        <v>562</v>
       </c>
       <c r="B26" t="s">
-        <v>533</v>
+        <v>600</v>
       </c>
       <c r="C26" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D26" t="s">
-        <v>423</v>
+        <v>589</v>
       </c>
       <c r="E26" t="s">
         <v>150</v>
@@ -10446,28 +10650,28 @@
       <c r="F26" t="s">
         <v>150</v>
       </c>
-      <c r="G26" t="s">
-        <v>197</v>
+      <c r="G26" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75">
       <c r="A27" t="s">
-        <v>440</v>
+        <v>576</v>
       </c>
       <c r="B27" t="s">
-        <v>534</v>
+        <v>599</v>
       </c>
       <c r="C27" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D27" t="s">
-        <v>423</v>
+        <v>589</v>
       </c>
       <c r="E27" t="s">
         <v>150</v>
@@ -10475,28 +10679,28 @@
       <c r="F27" t="s">
         <v>150</v>
       </c>
-      <c r="G27" t="s">
-        <v>197</v>
+      <c r="G27" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75">
       <c r="A28" t="s">
-        <v>441</v>
+        <v>577</v>
       </c>
       <c r="B28" t="s">
-        <v>535</v>
+        <v>598</v>
       </c>
       <c r="C28" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D28" t="s">
-        <v>423</v>
+        <v>611</v>
       </c>
       <c r="E28" t="s">
         <v>150</v>
@@ -10504,28 +10708,28 @@
       <c r="F28" t="s">
         <v>150</v>
       </c>
-      <c r="G28" t="s">
-        <v>197</v>
+      <c r="G28" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75">
       <c r="A29" t="s">
-        <v>442</v>
+        <v>578</v>
       </c>
       <c r="B29" t="s">
-        <v>536</v>
+        <v>612</v>
       </c>
       <c r="C29" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D29" t="s">
-        <v>423</v>
+        <v>613</v>
       </c>
       <c r="E29" t="s">
         <v>150</v>
@@ -10533,28 +10737,28 @@
       <c r="F29" t="s">
         <v>150</v>
       </c>
-      <c r="G29" t="s">
-        <v>197</v>
+      <c r="G29" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75">
       <c r="A30" t="s">
-        <v>443</v>
+        <v>579</v>
       </c>
       <c r="B30" t="s">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="C30" t="s">
-        <v>518</v>
+        <v>383</v>
       </c>
       <c r="D30" t="s">
-        <v>423</v>
+        <v>613</v>
       </c>
       <c r="E30" t="s">
         <v>150</v>
@@ -10562,28 +10766,28 @@
       <c r="F30" t="s">
         <v>150</v>
       </c>
-      <c r="G30" t="s">
-        <v>197</v>
+      <c r="G30" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75">
       <c r="A31" t="s">
-        <v>444</v>
+        <v>580</v>
       </c>
       <c r="B31" t="s">
-        <v>538</v>
+        <v>596</v>
       </c>
       <c r="C31" t="s">
-        <v>518</v>
+        <v>392</v>
       </c>
       <c r="D31" t="s">
-        <v>423</v>
+        <v>614</v>
       </c>
       <c r="E31" t="s">
         <v>150</v>
@@ -10591,25 +10795,28 @@
       <c r="F31" t="s">
         <v>150</v>
       </c>
-      <c r="G31" t="s">
-        <v>197</v>
+      <c r="G31" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75">
       <c r="A32" t="s">
-        <v>445</v>
+        <v>581</v>
       </c>
       <c r="B32" t="s">
-        <v>446</v>
+        <v>595</v>
+      </c>
+      <c r="C32" t="s">
+        <v>392</v>
       </c>
       <c r="D32" t="s">
-        <v>423</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
         <v>150</v>
@@ -10617,998 +10824,14 @@
       <c r="F32" t="s">
         <v>150</v>
       </c>
-      <c r="G32" t="s">
-        <v>197</v>
+      <c r="G32" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>447</v>
-      </c>
-      <c r="B33" t="s">
-        <v>448</v>
-      </c>
-      <c r="D33" t="s">
-        <v>408</v>
-      </c>
-      <c r="E33" t="s">
-        <v>150</v>
-      </c>
-      <c r="F33" t="s">
-        <v>150</v>
-      </c>
-      <c r="G33" t="s">
-        <v>197</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>449</v>
-      </c>
-      <c r="B34" t="s">
-        <v>450</v>
-      </c>
-      <c r="D34" t="s">
-        <v>408</v>
-      </c>
-      <c r="E34" t="s">
-        <v>150</v>
-      </c>
-      <c r="F34" t="s">
-        <v>150</v>
-      </c>
-      <c r="G34" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>451</v>
-      </c>
-      <c r="B35" t="s">
-        <v>539</v>
-      </c>
-      <c r="C35" t="s">
-        <v>518</v>
-      </c>
-      <c r="D35" t="s">
-        <v>423</v>
-      </c>
-      <c r="E35" t="s">
-        <v>150</v>
-      </c>
-      <c r="F35" t="s">
-        <v>150</v>
-      </c>
-      <c r="G35" t="s">
-        <v>197</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" t="s">
-        <v>452</v>
-      </c>
-      <c r="B36" t="s">
-        <v>453</v>
-      </c>
-      <c r="D36" t="s">
-        <v>423</v>
-      </c>
-      <c r="E36" t="s">
-        <v>150</v>
-      </c>
-      <c r="F36" t="s">
-        <v>150</v>
-      </c>
-      <c r="G36" t="s">
-        <v>197</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>454</v>
-      </c>
-      <c r="B37" t="s">
-        <v>455</v>
-      </c>
-      <c r="D37" t="s">
-        <v>408</v>
-      </c>
-      <c r="E37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F37" t="s">
-        <v>150</v>
-      </c>
-      <c r="G37" t="s">
-        <v>197</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>456</v>
-      </c>
-      <c r="B38" t="s">
-        <v>457</v>
-      </c>
-      <c r="D38" t="s">
-        <v>423</v>
-      </c>
-      <c r="E38" t="s">
-        <v>150</v>
-      </c>
-      <c r="F38" t="s">
-        <v>150</v>
-      </c>
-      <c r="G38" t="s">
-        <v>197</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>458</v>
-      </c>
-      <c r="B39" t="s">
-        <v>459</v>
-      </c>
-      <c r="D39" t="s">
-        <v>408</v>
-      </c>
-      <c r="E39" t="s">
-        <v>150</v>
-      </c>
-      <c r="F39" t="s">
-        <v>150</v>
-      </c>
-      <c r="G39" t="s">
-        <v>197</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" t="s">
-        <v>460</v>
-      </c>
-      <c r="B40" t="s">
-        <v>461</v>
-      </c>
-      <c r="D40" t="s">
-        <v>423</v>
-      </c>
-      <c r="E40" t="s">
-        <v>150</v>
-      </c>
-      <c r="F40" t="s">
-        <v>150</v>
-      </c>
-      <c r="G40" t="s">
-        <v>197</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" t="s">
-        <v>462</v>
-      </c>
-      <c r="B41" t="s">
-        <v>463</v>
-      </c>
-      <c r="D41" t="s">
-        <v>408</v>
-      </c>
-      <c r="E41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F41" t="s">
-        <v>150</v>
-      </c>
-      <c r="G41" t="s">
-        <v>197</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>464</v>
-      </c>
-      <c r="B42" t="s">
-        <v>465</v>
-      </c>
-      <c r="D42" t="s">
-        <v>423</v>
-      </c>
-      <c r="E42" t="s">
-        <v>150</v>
-      </c>
-      <c r="F42" t="s">
-        <v>150</v>
-      </c>
-      <c r="G42" t="s">
-        <v>197</v>
-      </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
-      <c r="I42" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" t="s">
-        <v>466</v>
-      </c>
-      <c r="B43" t="s">
-        <v>467</v>
-      </c>
-      <c r="D43" t="s">
-        <v>423</v>
-      </c>
-      <c r="E43" t="s">
-        <v>150</v>
-      </c>
-      <c r="F43" t="s">
-        <v>150</v>
-      </c>
-      <c r="G43" t="s">
-        <v>197</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" t="s">
-        <v>468</v>
-      </c>
-      <c r="B44" t="s">
-        <v>469</v>
-      </c>
-      <c r="D44" t="s">
-        <v>408</v>
-      </c>
-      <c r="E44" t="s">
-        <v>150</v>
-      </c>
-      <c r="F44" t="s">
-        <v>150</v>
-      </c>
-      <c r="G44" t="s">
-        <v>197</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" t="s">
-        <v>470</v>
-      </c>
-      <c r="B45" t="s">
-        <v>471</v>
-      </c>
-      <c r="D45" t="s">
-        <v>408</v>
-      </c>
-      <c r="E45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F45" t="s">
-        <v>150</v>
-      </c>
-      <c r="G45" t="s">
-        <v>197</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" t="s">
-        <v>472</v>
-      </c>
-      <c r="B46" t="s">
-        <v>540</v>
-      </c>
-      <c r="C46" t="s">
-        <v>518</v>
-      </c>
-      <c r="D46" t="s">
-        <v>423</v>
-      </c>
-      <c r="E46" t="s">
-        <v>150</v>
-      </c>
-      <c r="F46" t="s">
-        <v>150</v>
-      </c>
-      <c r="G46" t="s">
-        <v>197</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" t="s">
-        <v>473</v>
-      </c>
-      <c r="B47" t="s">
-        <v>541</v>
-      </c>
-      <c r="C47" t="s">
-        <v>518</v>
-      </c>
-      <c r="D47" t="s">
-        <v>423</v>
-      </c>
-      <c r="E47" t="s">
-        <v>150</v>
-      </c>
-      <c r="F47" t="s">
-        <v>150</v>
-      </c>
-      <c r="G47" t="s">
-        <v>197</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" t="s">
-        <v>474</v>
-      </c>
-      <c r="B48" t="s">
-        <v>542</v>
-      </c>
-      <c r="C48" t="s">
-        <v>518</v>
-      </c>
-      <c r="D48" t="s">
-        <v>423</v>
-      </c>
-      <c r="E48" t="s">
-        <v>150</v>
-      </c>
-      <c r="F48" t="s">
-        <v>150</v>
-      </c>
-      <c r="G48" t="s">
-        <v>197</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" t="s">
-        <v>475</v>
-      </c>
-      <c r="B49" t="s">
-        <v>476</v>
-      </c>
-      <c r="D49" t="s">
-        <v>423</v>
-      </c>
-      <c r="E49" t="s">
-        <v>150</v>
-      </c>
-      <c r="F49" t="s">
-        <v>150</v>
-      </c>
-      <c r="G49" t="s">
-        <v>197</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" t="s">
-        <v>477</v>
-      </c>
-      <c r="B50" t="s">
-        <v>543</v>
-      </c>
-      <c r="C50" t="s">
-        <v>518</v>
-      </c>
-      <c r="D50" t="s">
-        <v>423</v>
-      </c>
-      <c r="E50" t="s">
-        <v>150</v>
-      </c>
-      <c r="F50" t="s">
-        <v>150</v>
-      </c>
-      <c r="G50" t="s">
-        <v>197</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" t="s">
-        <v>478</v>
-      </c>
-      <c r="B51" t="s">
-        <v>544</v>
-      </c>
-      <c r="C51" t="s">
-        <v>518</v>
-      </c>
-      <c r="D51" t="s">
-        <v>423</v>
-      </c>
-      <c r="E51" t="s">
-        <v>150</v>
-      </c>
-      <c r="F51" t="s">
-        <v>150</v>
-      </c>
-      <c r="G51" t="s">
-        <v>197</v>
-      </c>
-      <c r="H51">
-        <v>1</v>
-      </c>
-      <c r="I51" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" t="s">
-        <v>479</v>
-      </c>
-      <c r="B52" t="s">
-        <v>507</v>
-      </c>
-      <c r="C52" t="s">
-        <v>517</v>
-      </c>
-      <c r="E52" t="s">
-        <v>150</v>
-      </c>
-      <c r="F52" t="s">
-        <v>150</v>
-      </c>
-      <c r="G52" t="s">
-        <v>197</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" t="s">
-        <v>480</v>
-      </c>
-      <c r="B53" t="s">
-        <v>511</v>
-      </c>
-      <c r="C53" t="s">
-        <v>517</v>
-      </c>
-      <c r="D53" t="s">
-        <v>408</v>
-      </c>
-      <c r="E53" t="s">
-        <v>150</v>
-      </c>
-      <c r="F53" t="s">
-        <v>150</v>
-      </c>
-      <c r="G53" t="s">
-        <v>197</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" t="s">
-        <v>481</v>
-      </c>
-      <c r="B54" t="s">
-        <v>506</v>
-      </c>
-      <c r="C54" t="s">
-        <v>517</v>
-      </c>
-      <c r="D54" t="s">
-        <v>408</v>
-      </c>
-      <c r="E54" t="s">
-        <v>150</v>
-      </c>
-      <c r="F54" t="s">
-        <v>150</v>
-      </c>
-      <c r="G54" t="s">
-        <v>197</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" t="s">
-        <v>482</v>
-      </c>
-      <c r="B55" t="s">
-        <v>483</v>
-      </c>
-      <c r="C55" t="s">
-        <v>517</v>
-      </c>
-      <c r="D55" t="s">
-        <v>419</v>
-      </c>
-      <c r="E55" t="s">
-        <v>150</v>
-      </c>
-      <c r="F55" t="s">
-        <v>150</v>
-      </c>
-      <c r="G55" t="s">
-        <v>197</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" t="s">
-        <v>484</v>
-      </c>
-      <c r="B56" t="s">
-        <v>485</v>
-      </c>
-      <c r="C56" t="s">
-        <v>517</v>
-      </c>
-      <c r="D56" t="s">
-        <v>408</v>
-      </c>
-      <c r="E56" t="s">
-        <v>150</v>
-      </c>
-      <c r="F56" t="s">
-        <v>150</v>
-      </c>
-      <c r="G56" t="s">
-        <v>197</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" t="s">
-        <v>486</v>
-      </c>
-      <c r="B57" t="s">
-        <v>487</v>
-      </c>
-      <c r="C57" t="s">
-        <v>517</v>
-      </c>
-      <c r="D57" t="s">
-        <v>408</v>
-      </c>
-      <c r="E57" t="s">
-        <v>150</v>
-      </c>
-      <c r="F57" t="s">
-        <v>150</v>
-      </c>
-      <c r="G57" t="s">
-        <v>197</v>
-      </c>
-      <c r="H57">
-        <v>1</v>
-      </c>
-      <c r="I57" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" t="s">
-        <v>488</v>
-      </c>
-      <c r="B58" t="s">
-        <v>513</v>
-      </c>
-      <c r="C58" t="s">
-        <v>517</v>
-      </c>
-      <c r="D58" t="s">
-        <v>408</v>
-      </c>
-      <c r="E58" t="s">
-        <v>150</v>
-      </c>
-      <c r="F58" t="s">
-        <v>150</v>
-      </c>
-      <c r="G58" t="s">
-        <v>197</v>
-      </c>
-      <c r="H58">
-        <v>1</v>
-      </c>
-      <c r="I58" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" t="s">
-        <v>489</v>
-      </c>
-      <c r="B59" t="s">
-        <v>512</v>
-      </c>
-      <c r="C59" t="s">
-        <v>517</v>
-      </c>
-      <c r="D59" t="s">
-        <v>490</v>
-      </c>
-      <c r="E59" t="s">
-        <v>150</v>
-      </c>
-      <c r="F59" t="s">
-        <v>150</v>
-      </c>
-      <c r="G59" t="s">
-        <v>197</v>
-      </c>
-      <c r="H59">
-        <v>1</v>
-      </c>
-      <c r="I59" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" t="s">
-        <v>491</v>
-      </c>
-      <c r="B60" t="s">
-        <v>508</v>
-      </c>
-      <c r="C60" t="s">
-        <v>517</v>
-      </c>
-      <c r="D60" t="s">
-        <v>492</v>
-      </c>
-      <c r="E60" t="s">
-        <v>150</v>
-      </c>
-      <c r="F60" t="s">
-        <v>150</v>
-      </c>
-      <c r="G60" t="s">
-        <v>197</v>
-      </c>
-      <c r="H60">
-        <v>1</v>
-      </c>
-      <c r="I60" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" t="s">
-        <v>493</v>
-      </c>
-      <c r="B61" t="s">
-        <v>509</v>
-      </c>
-      <c r="C61" t="s">
-        <v>517</v>
-      </c>
-      <c r="D61" t="s">
-        <v>492</v>
-      </c>
-      <c r="E61" t="s">
-        <v>150</v>
-      </c>
-      <c r="F61" t="s">
-        <v>150</v>
-      </c>
-      <c r="G61" t="s">
-        <v>197</v>
-      </c>
-      <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" t="s">
-        <v>494</v>
-      </c>
-      <c r="B62" t="s">
-        <v>510</v>
-      </c>
-      <c r="C62" t="s">
-        <v>517</v>
-      </c>
-      <c r="D62" t="s">
-        <v>492</v>
-      </c>
-      <c r="E62" t="s">
-        <v>150</v>
-      </c>
-      <c r="F62" t="s">
-        <v>150</v>
-      </c>
-      <c r="G62" t="s">
-        <v>197</v>
-      </c>
-      <c r="H62">
-        <v>1</v>
-      </c>
-      <c r="I62" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" t="s">
-        <v>495</v>
-      </c>
-      <c r="B63" t="s">
-        <v>496</v>
-      </c>
-      <c r="C63" t="s">
-        <v>517</v>
-      </c>
-      <c r="D63" t="s">
-        <v>497</v>
-      </c>
-      <c r="E63" t="s">
-        <v>150</v>
-      </c>
-      <c r="F63" t="s">
-        <v>150</v>
-      </c>
-      <c r="G63" t="s">
-        <v>197</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" t="s">
-        <v>498</v>
-      </c>
-      <c r="B64" t="s">
-        <v>499</v>
-      </c>
-      <c r="C64" t="s">
-        <v>517</v>
-      </c>
-      <c r="D64" t="s">
-        <v>497</v>
-      </c>
-      <c r="E64" t="s">
-        <v>150</v>
-      </c>
-      <c r="F64" t="s">
-        <v>150</v>
-      </c>
-      <c r="G64" t="s">
-        <v>197</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" t="s">
-        <v>500</v>
-      </c>
-      <c r="B65" t="s">
-        <v>515</v>
-      </c>
-      <c r="E65" t="s">
-        <v>150</v>
-      </c>
-      <c r="F65" t="s">
-        <v>150</v>
-      </c>
-      <c r="G65" t="s">
-        <v>197</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" t="s">
-        <v>501</v>
-      </c>
-      <c r="B66" t="s">
-        <v>514</v>
-      </c>
-      <c r="E66" t="s">
-        <v>150</v>
-      </c>
-      <c r="F66" t="s">
-        <v>150</v>
-      </c>
-      <c r="G66" t="s">
-        <v>197</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" t="s">
-        <v>502</v>
-      </c>
-      <c r="B67" t="s">
-        <v>516</v>
-      </c>
-      <c r="E67" t="s">
-        <v>150</v>
-      </c>
-      <c r="F67" t="s">
-        <v>150</v>
-      </c>
-      <c r="G67" t="s">
-        <v>197</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" t="s">
-        <v>503</v>
-      </c>
-      <c r="B68" t="s">
-        <v>504</v>
-      </c>
-      <c r="C68" t="s">
-        <v>517</v>
-      </c>
-      <c r="D68" t="s">
-        <v>505</v>
-      </c>
-      <c r="E68" t="s">
-        <v>150</v>
-      </c>
-      <c r="F68" t="s">
-        <v>150</v>
-      </c>
-      <c r="G68" t="s">
-        <v>197</v>
-      </c>
-      <c r="H68">
-        <v>1</v>
-      </c>
-      <c r="I68" t="s">
-        <v>400</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
